--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748474</v>
+        <v>122748953</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578871</v>
+        <v>578965</v>
       </c>
       <c r="R2" t="n">
-        <v>6428320</v>
+        <v>6428213</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748530</v>
+        <v>122748802</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578887</v>
+        <v>578916</v>
       </c>
       <c r="R3" t="n">
-        <v>6428305</v>
+        <v>6428228</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748719</v>
+        <v>122748650</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578907</v>
+        <v>578934</v>
       </c>
       <c r="R4" t="n">
-        <v>6428320</v>
+        <v>6428344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748554</v>
+        <v>122748796</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1023,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578876</v>
+        <v>578916</v>
       </c>
       <c r="R5" t="n">
-        <v>6428319</v>
+        <v>6428228</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748838</v>
+        <v>122748871</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578919</v>
+        <v>578921</v>
       </c>
       <c r="R6" t="n">
-        <v>6428218</v>
+        <v>6428203</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748513</v>
+        <v>122748770</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578874</v>
+        <v>578907</v>
       </c>
       <c r="R7" t="n">
-        <v>6428309</v>
+        <v>6428303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748796</v>
+        <v>122748710</v>
       </c>
       <c r="B8" t="n">
-        <v>57537</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578916</v>
+        <v>578908</v>
       </c>
       <c r="R8" t="n">
-        <v>6428228</v>
+        <v>6428300</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748608</v>
+        <v>122748865</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578920</v>
+        <v>578923</v>
       </c>
       <c r="R9" t="n">
-        <v>6428319</v>
+        <v>6428196</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748939</v>
+        <v>122748554</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578966</v>
+        <v>578876</v>
       </c>
       <c r="R10" t="n">
-        <v>6428216</v>
+        <v>6428319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748570</v>
+        <v>122748939</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578855</v>
+        <v>578966</v>
       </c>
       <c r="R11" t="n">
-        <v>6428305</v>
+        <v>6428216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748770</v>
+        <v>122748778</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>95118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,33 +1803,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1902,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748974</v>
+        <v>122748491</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578879</v>
+        <v>578872</v>
       </c>
       <c r="R13" t="n">
-        <v>6428307</v>
+        <v>6428318</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748953</v>
+        <v>122748669</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>91350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2021,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578965</v>
+        <v>578951</v>
       </c>
       <c r="R14" t="n">
-        <v>6428213</v>
+        <v>6428317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748491</v>
+        <v>122748878</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578872</v>
+        <v>578923</v>
       </c>
       <c r="R15" t="n">
-        <v>6428318</v>
+        <v>6428199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748891</v>
+        <v>122748749</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578919</v>
+        <v>578854</v>
       </c>
       <c r="R16" t="n">
-        <v>6428209</v>
+        <v>6428300</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748749</v>
+        <v>122748974</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,10 +2393,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578854</v>
+        <v>578879</v>
       </c>
       <c r="R17" t="n">
-        <v>6428300</v>
+        <v>6428307</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748625</v>
+        <v>122748530</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578926</v>
+        <v>578887</v>
       </c>
       <c r="R18" t="n">
-        <v>6428331</v>
+        <v>6428305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748817</v>
+        <v>122748692</v>
       </c>
       <c r="B19" t="n">
-        <v>56594</v>
+        <v>98347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,35 +2579,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2616,13 +2615,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578912</v>
+        <v>578948</v>
       </c>
       <c r="R19" t="n">
-        <v>6428250</v>
+        <v>6428315</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,6 +2659,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748692</v>
+        <v>122748450</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578948</v>
+        <v>578855</v>
       </c>
       <c r="R20" t="n">
-        <v>6428315</v>
+        <v>6428306</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748802</v>
+        <v>122748637</v>
       </c>
       <c r="B21" t="n">
-        <v>57754</v>
+        <v>98347</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2801,39 +2801,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2841,13 +2837,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578916</v>
+        <v>578855</v>
       </c>
       <c r="R21" t="n">
-        <v>6428228</v>
+        <v>6428305</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,6 +2881,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2903,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748922</v>
+        <v>122748608</v>
       </c>
       <c r="B22" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,14 +2944,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578971</v>
+        <v>578920</v>
       </c>
       <c r="R22" t="n">
-        <v>6428217</v>
+        <v>6428319</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3014,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748903</v>
+        <v>122748852</v>
       </c>
       <c r="B23" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578994</v>
+        <v>578925</v>
       </c>
       <c r="R23" t="n">
-        <v>6428205</v>
+        <v>6428192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748450</v>
+        <v>122748513</v>
       </c>
       <c r="B24" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3173,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578855</v>
+        <v>578874</v>
       </c>
       <c r="R24" t="n">
-        <v>6428306</v>
+        <v>6428309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3236,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748778</v>
+        <v>122748817</v>
       </c>
       <c r="B25" t="n">
-        <v>95015</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,27 +3249,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3280,13 +3281,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578907</v>
+        <v>578912</v>
       </c>
       <c r="R25" t="n">
-        <v>6428303</v>
+        <v>6428250</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3325,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748710</v>
+        <v>122748891</v>
       </c>
       <c r="B26" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578908</v>
+        <v>578919</v>
       </c>
       <c r="R26" t="n">
-        <v>6428300</v>
+        <v>6428209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748865</v>
+        <v>122748474</v>
       </c>
       <c r="B27" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578923</v>
+        <v>578871</v>
       </c>
       <c r="R27" t="n">
-        <v>6428196</v>
+        <v>6428320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748871</v>
+        <v>122748824</v>
       </c>
       <c r="B28" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578921</v>
+        <v>578919</v>
       </c>
       <c r="R28" t="n">
-        <v>6428203</v>
+        <v>6428210</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748878</v>
+        <v>122748922</v>
       </c>
       <c r="B29" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,14 +3720,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578923</v>
+        <v>578971</v>
       </c>
       <c r="R29" t="n">
-        <v>6428199</v>
+        <v>6428217</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748650</v>
+        <v>122748625</v>
       </c>
       <c r="B30" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578934</v>
+        <v>578926</v>
       </c>
       <c r="R30" t="n">
-        <v>6428344</v>
+        <v>6428331</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748824</v>
+        <v>122748903</v>
       </c>
       <c r="B31" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578919</v>
+        <v>578994</v>
       </c>
       <c r="R31" t="n">
-        <v>6428210</v>
+        <v>6428205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748669</v>
+        <v>122748838</v>
       </c>
       <c r="B32" t="n">
-        <v>91247</v>
+        <v>57494</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4021,25 +4021,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4047,12 +4047,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4060,13 +4061,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578951</v>
+        <v>578919</v>
       </c>
       <c r="R32" t="n">
-        <v>6428317</v>
+        <v>6428218</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4104,7 +4105,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748852</v>
+        <v>122748719</v>
       </c>
       <c r="B33" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578925</v>
+        <v>578907</v>
       </c>
       <c r="R33" t="n">
-        <v>6428192</v>
+        <v>6428320</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4231,6 +4231,3671 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122832846</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>578992</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6428165</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122832550</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>578934</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6428155</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122832884</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>578944</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6428183</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122832077</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>578858</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6428260</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122832101</v>
+      </c>
+      <c r="B38" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>578875</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6428259</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122831868</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>578848</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6428302</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122832231</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>578889</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6428243</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122832383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>578929</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6428202</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122832702</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>578972</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6428239</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122832686</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>578971</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6428232</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122832675</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>578924</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6428234</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122833108</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>578912</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6428250</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122832662</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>578900</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6428250</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122832254</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>578889</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6428248</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122832400</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>578935</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6428215</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122832436</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>578943</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6428212</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122832134</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>578881</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6428255</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122832563</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>578948</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6428141</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122832650</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>578917</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6428142</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122832208</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>578887</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6428260</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122832456</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>578914</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6428200</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122832341</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>578917</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6428212</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122832784</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>578994</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6428231</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122832157</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>578886</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6428255</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122832592</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>578925</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6428157</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122832817</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>578996</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6428222</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122832530</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>578925</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6428178</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122832768</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>578986</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6428221</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122832655</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>578894</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6428171</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122831927</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>578836</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6428289</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122832730</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>578971</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6428216</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122832750</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>578986</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6428201</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122832295</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>A 5838, Överum, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>578916</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6428220</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748953</v>
+        <v>122748796</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578965</v>
+        <v>578916</v>
       </c>
       <c r="R2" t="n">
-        <v>6428213</v>
+        <v>6428228</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748802</v>
+        <v>122748871</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578916</v>
+        <v>578921</v>
       </c>
       <c r="R3" t="n">
-        <v>6428228</v>
+        <v>6428203</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748650</v>
+        <v>122748878</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578934</v>
+        <v>578923</v>
       </c>
       <c r="R4" t="n">
-        <v>6428344</v>
+        <v>6428199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748796</v>
+        <v>122748922</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,53 +1023,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578916</v>
+        <v>578971</v>
       </c>
       <c r="R5" t="n">
-        <v>6428228</v>
+        <v>6428217</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748871</v>
+        <v>122748953</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578921</v>
+        <v>578965</v>
       </c>
       <c r="R6" t="n">
-        <v>6428203</v>
+        <v>6428213</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748770</v>
+        <v>122748903</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578907</v>
+        <v>578994</v>
       </c>
       <c r="R7" t="n">
-        <v>6428303</v>
+        <v>6428205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748710</v>
+        <v>122748530</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578908</v>
+        <v>578887</v>
       </c>
       <c r="R8" t="n">
-        <v>6428300</v>
+        <v>6428305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748865</v>
+        <v>122748637</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578923</v>
+        <v>578855</v>
       </c>
       <c r="R9" t="n">
-        <v>6428196</v>
+        <v>6428305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748554</v>
+        <v>122748778</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>95126</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,33 +1578,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1617,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578876</v>
+        <v>578907</v>
       </c>
       <c r="R10" t="n">
-        <v>6428319</v>
+        <v>6428303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748939</v>
+        <v>122748891</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578966</v>
+        <v>578919</v>
       </c>
       <c r="R11" t="n">
-        <v>6428216</v>
+        <v>6428209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748778</v>
+        <v>122748625</v>
       </c>
       <c r="B12" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,29 +1796,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1835,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578907</v>
+        <v>578926</v>
       </c>
       <c r="R12" t="n">
-        <v>6428303</v>
+        <v>6428331</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1898,7 @@
         <v>122748491</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2009,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748669</v>
+        <v>122748865</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,38 +2018,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2060,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578951</v>
+        <v>578923</v>
       </c>
       <c r="R14" t="n">
-        <v>6428317</v>
+        <v>6428196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748878</v>
+        <v>122748554</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578923</v>
+        <v>578876</v>
       </c>
       <c r="R15" t="n">
-        <v>6428199</v>
+        <v>6428319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748749</v>
+        <v>122748802</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>57848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,35 +2240,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2282,13 +2280,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578854</v>
+        <v>578916</v>
       </c>
       <c r="R16" t="n">
-        <v>6428300</v>
+        <v>6428228</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2324,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2345,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748974</v>
+        <v>122748824</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578879</v>
+        <v>578919</v>
       </c>
       <c r="R17" t="n">
-        <v>6428307</v>
+        <v>6428210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748530</v>
+        <v>122748710</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578887</v>
+        <v>578908</v>
       </c>
       <c r="R18" t="n">
-        <v>6428305</v>
+        <v>6428300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748692</v>
+        <v>122748474</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578948</v>
+        <v>578871</v>
       </c>
       <c r="R19" t="n">
-        <v>6428315</v>
+        <v>6428320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748450</v>
+        <v>122748669</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,35 +2687,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578855</v>
+        <v>578951</v>
       </c>
       <c r="R20" t="n">
-        <v>6428306</v>
+        <v>6428317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748637</v>
+        <v>122748513</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578855</v>
+        <v>578874</v>
       </c>
       <c r="R21" t="n">
-        <v>6428305</v>
+        <v>6428309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748608</v>
+        <v>122748450</v>
       </c>
       <c r="B22" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578920</v>
+        <v>578855</v>
       </c>
       <c r="R22" t="n">
-        <v>6428319</v>
+        <v>6428306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748852</v>
+        <v>122748700</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578925</v>
+        <v>578948</v>
       </c>
       <c r="R23" t="n">
-        <v>6428192</v>
+        <v>6428315</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748513</v>
+        <v>122748939</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578874</v>
+        <v>578966</v>
       </c>
       <c r="R24" t="n">
-        <v>6428309</v>
+        <v>6428216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748817</v>
+        <v>122748770</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,35 +3245,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3281,13 +3281,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578912</v>
+        <v>578907</v>
       </c>
       <c r="R25" t="n">
-        <v>6428250</v>
+        <v>6428303</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3325,6 +3325,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748891</v>
+        <v>122748974</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578919</v>
+        <v>578879</v>
       </c>
       <c r="R26" t="n">
-        <v>6428209</v>
+        <v>6428307</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748474</v>
+        <v>122748817</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3466,35 +3467,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3502,13 +3503,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578871</v>
+        <v>578912</v>
       </c>
       <c r="R27" t="n">
-        <v>6428320</v>
+        <v>6428250</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3546,7 +3547,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748824</v>
+        <v>122748749</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578919</v>
+        <v>578854</v>
       </c>
       <c r="R28" t="n">
-        <v>6428210</v>
+        <v>6428300</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748922</v>
+        <v>122748650</v>
       </c>
       <c r="B29" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,14 +3720,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578971</v>
+        <v>578934</v>
       </c>
       <c r="R29" t="n">
-        <v>6428217</v>
+        <v>6428344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748625</v>
+        <v>122748608</v>
       </c>
       <c r="B30" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578926</v>
+        <v>578920</v>
       </c>
       <c r="R30" t="n">
-        <v>6428331</v>
+        <v>6428319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748903</v>
+        <v>122748719</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578994</v>
+        <v>578907</v>
       </c>
       <c r="R31" t="n">
-        <v>6428205</v>
+        <v>6428320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748719</v>
+        <v>122748852</v>
       </c>
       <c r="B33" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578907</v>
+        <v>578925</v>
       </c>
       <c r="R33" t="n">
-        <v>6428320</v>
+        <v>6428192</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832846</v>
+        <v>122832750</v>
       </c>
       <c r="B34" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578992</v>
+        <v>578986</v>
       </c>
       <c r="R34" t="n">
-        <v>6428165</v>
+        <v>6428201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832550</v>
+        <v>122832101</v>
       </c>
       <c r="B35" t="n">
-        <v>98347</v>
+        <v>95126</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4357,33 +4357,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4393,10 +4389,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578934</v>
+        <v>578875</v>
       </c>
       <c r="R35" t="n">
-        <v>6428155</v>
+        <v>6428259</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,7 +4455,7 @@
         <v>122832884</v>
       </c>
       <c r="B36" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4567,10 +4563,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832077</v>
+        <v>122832563</v>
       </c>
       <c r="B37" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4615,10 +4611,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578858</v>
+        <v>578948</v>
       </c>
       <c r="R37" t="n">
-        <v>6428260</v>
+        <v>6428141</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,10 +4674,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832101</v>
+        <v>122832400</v>
       </c>
       <c r="B38" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4690,29 +4686,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578875</v>
+        <v>578935</v>
       </c>
       <c r="R38" t="n">
-        <v>6428259</v>
+        <v>6428215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122831868</v>
+        <v>122832254</v>
       </c>
       <c r="B39" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578848</v>
+        <v>578889</v>
       </c>
       <c r="R39" t="n">
-        <v>6428302</v>
+        <v>6428248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832231</v>
+        <v>122832592</v>
       </c>
       <c r="B40" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578889</v>
+        <v>578925</v>
       </c>
       <c r="R40" t="n">
-        <v>6428243</v>
+        <v>6428157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832383</v>
+        <v>122832675</v>
       </c>
       <c r="B41" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578929</v>
+        <v>578924</v>
       </c>
       <c r="R41" t="n">
-        <v>6428202</v>
+        <v>6428234</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832702</v>
+        <v>122832383</v>
       </c>
       <c r="B42" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578972</v>
+        <v>578929</v>
       </c>
       <c r="R42" t="n">
-        <v>6428239</v>
+        <v>6428202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832686</v>
+        <v>122832436</v>
       </c>
       <c r="B43" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5241,35 +5241,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5277,13 +5281,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578971</v>
+        <v>578943</v>
       </c>
       <c r="R43" t="n">
-        <v>6428232</v>
+        <v>6428212</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5321,7 +5325,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5340,10 +5343,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832675</v>
+        <v>122832295</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5388,10 +5391,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578924</v>
+        <v>578916</v>
       </c>
       <c r="R44" t="n">
-        <v>6428234</v>
+        <v>6428220</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5451,10 +5454,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122833108</v>
+        <v>122832208</v>
       </c>
       <c r="B45" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5463,39 +5466,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5503,13 +5502,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578912</v>
+        <v>578887</v>
       </c>
       <c r="R45" t="n">
-        <v>6428250</v>
+        <v>6428260</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5547,6 +5546,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5565,10 +5565,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832662</v>
+        <v>122832945</v>
       </c>
       <c r="B46" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578900</v>
+        <v>578992</v>
       </c>
       <c r="R46" t="n">
-        <v>6428250</v>
+        <v>6428165</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5676,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832254</v>
+        <v>122832686</v>
       </c>
       <c r="B47" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578889</v>
+        <v>578971</v>
       </c>
       <c r="R47" t="n">
-        <v>6428248</v>
+        <v>6428232</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832400</v>
+        <v>122832231</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578935</v>
+        <v>578889</v>
       </c>
       <c r="R48" t="n">
-        <v>6428215</v>
+        <v>6428243</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832436</v>
+        <v>122832768</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5910,39 +5910,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5950,13 +5946,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578943</v>
+        <v>578986</v>
       </c>
       <c r="R49" t="n">
-        <v>6428212</v>
+        <v>6428221</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5994,6 +5990,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6012,10 +6009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832134</v>
+        <v>122832817</v>
       </c>
       <c r="B50" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6060,10 +6057,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578881</v>
+        <v>578996</v>
       </c>
       <c r="R50" t="n">
-        <v>6428255</v>
+        <v>6428222</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6123,10 +6120,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832563</v>
+        <v>122832784</v>
       </c>
       <c r="B51" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6171,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578948</v>
+        <v>578994</v>
       </c>
       <c r="R51" t="n">
-        <v>6428141</v>
+        <v>6428231</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6234,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832650</v>
+        <v>122832456</v>
       </c>
       <c r="B52" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6282,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578917</v>
+        <v>578914</v>
       </c>
       <c r="R52" t="n">
-        <v>6428142</v>
+        <v>6428200</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832208</v>
+        <v>122832341</v>
       </c>
       <c r="B53" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6393,10 +6390,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578887</v>
+        <v>578917</v>
       </c>
       <c r="R53" t="n">
-        <v>6428260</v>
+        <v>6428212</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6456,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832456</v>
+        <v>122832702</v>
       </c>
       <c r="B54" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6504,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578914</v>
+        <v>578972</v>
       </c>
       <c r="R54" t="n">
-        <v>6428200</v>
+        <v>6428239</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832341</v>
+        <v>122832655</v>
       </c>
       <c r="B55" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6615,10 +6612,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578917</v>
+        <v>578894</v>
       </c>
       <c r="R55" t="n">
-        <v>6428212</v>
+        <v>6428171</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6678,10 +6675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832784</v>
+        <v>122832730</v>
       </c>
       <c r="B56" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6726,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578994</v>
+        <v>578971</v>
       </c>
       <c r="R56" t="n">
-        <v>6428231</v>
+        <v>6428216</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6789,10 +6786,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832157</v>
+        <v>122833108</v>
       </c>
       <c r="B57" t="n">
-        <v>98347</v>
+        <v>57848</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6801,35 +6798,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6837,13 +6838,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578886</v>
+        <v>578912</v>
       </c>
       <c r="R57" t="n">
-        <v>6428255</v>
+        <v>6428250</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6881,7 +6882,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832592</v>
+        <v>122832530</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>578925</v>
       </c>
       <c r="R58" t="n">
-        <v>6428157</v>
+        <v>6428178</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832817</v>
+        <v>122831868</v>
       </c>
       <c r="B59" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578996</v>
+        <v>578848</v>
       </c>
       <c r="R59" t="n">
-        <v>6428222</v>
+        <v>6428302</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832530</v>
+        <v>122832077</v>
       </c>
       <c r="B60" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578925</v>
+        <v>578858</v>
       </c>
       <c r="R60" t="n">
-        <v>6428178</v>
+        <v>6428260</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832768</v>
+        <v>122832550</v>
       </c>
       <c r="B61" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578986</v>
+        <v>578934</v>
       </c>
       <c r="R61" t="n">
-        <v>6428221</v>
+        <v>6428155</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832655</v>
+        <v>122832157</v>
       </c>
       <c r="B62" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578894</v>
+        <v>578886</v>
       </c>
       <c r="R62" t="n">
-        <v>6428171</v>
+        <v>6428255</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7455,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122831927</v>
+        <v>122832662</v>
       </c>
       <c r="B63" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578836</v>
+        <v>578900</v>
       </c>
       <c r="R63" t="n">
-        <v>6428289</v>
+        <v>6428250</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832730</v>
+        <v>122832134</v>
       </c>
       <c r="B64" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578971</v>
+        <v>578881</v>
       </c>
       <c r="R64" t="n">
-        <v>6428216</v>
+        <v>6428255</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832750</v>
+        <v>122832650</v>
       </c>
       <c r="B65" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578986</v>
+        <v>578917</v>
       </c>
       <c r="R65" t="n">
-        <v>6428201</v>
+        <v>6428142</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832295</v>
+        <v>122831927</v>
       </c>
       <c r="B66" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578916</v>
+        <v>578836</v>
       </c>
       <c r="R66" t="n">
-        <v>6428220</v>
+        <v>6428289</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -2453,7 +2453,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748710</v>
+        <v>122748474</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578908</v>
+        <v>578871</v>
       </c>
       <c r="R18" t="n">
-        <v>6428300</v>
+        <v>6428320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748474</v>
+        <v>122748669</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,35 +2576,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2612,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578871</v>
+        <v>578951</v>
       </c>
       <c r="R19" t="n">
-        <v>6428320</v>
+        <v>6428317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748669</v>
+        <v>122748710</v>
       </c>
       <c r="B20" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,38 +2690,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578951</v>
+        <v>578908</v>
       </c>
       <c r="R20" t="n">
-        <v>6428317</v>
+        <v>6428300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748796</v>
+        <v>122748625</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578916</v>
+        <v>578926</v>
       </c>
       <c r="R2" t="n">
-        <v>6428228</v>
+        <v>6428331</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748871</v>
+        <v>122748710</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578921</v>
+        <v>578908</v>
       </c>
       <c r="R3" t="n">
-        <v>6428203</v>
+        <v>6428300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748878</v>
+        <v>122748669</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578923</v>
+        <v>578951</v>
       </c>
       <c r="R4" t="n">
-        <v>6428199</v>
+        <v>6428317</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748922</v>
+        <v>122748719</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1055,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578971</v>
+        <v>578907</v>
       </c>
       <c r="R5" t="n">
-        <v>6428217</v>
+        <v>6428320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748953</v>
+        <v>122748692</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578965</v>
+        <v>578948</v>
       </c>
       <c r="R6" t="n">
-        <v>6428213</v>
+        <v>6428315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748903</v>
+        <v>122748865</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578994</v>
+        <v>578923</v>
       </c>
       <c r="R7" t="n">
-        <v>6428205</v>
+        <v>6428196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748530</v>
+        <v>122748491</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578887</v>
+        <v>578872</v>
       </c>
       <c r="R8" t="n">
-        <v>6428305</v>
+        <v>6428318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748637</v>
+        <v>122748474</v>
       </c>
       <c r="B9" t="n">
         <v>98355</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578855</v>
+        <v>578871</v>
       </c>
       <c r="R9" t="n">
-        <v>6428305</v>
+        <v>6428320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748778</v>
+        <v>122748802</v>
       </c>
       <c r="B10" t="n">
-        <v>95126</v>
+        <v>57848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,27 +1582,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578907</v>
+        <v>578916</v>
       </c>
       <c r="R10" t="n">
-        <v>6428303</v>
+        <v>6428228</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1662,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1673,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748891</v>
+        <v>122748953</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1721,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578919</v>
+        <v>578965</v>
       </c>
       <c r="R11" t="n">
-        <v>6428209</v>
+        <v>6428213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748625</v>
+        <v>122748513</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1832,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578926</v>
+        <v>578874</v>
       </c>
       <c r="R12" t="n">
-        <v>6428331</v>
+        <v>6428309</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748491</v>
+        <v>122748796</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,35 +1914,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,13 +1954,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578872</v>
+        <v>578916</v>
       </c>
       <c r="R13" t="n">
-        <v>6428318</v>
+        <v>6428228</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +1998,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2006,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748865</v>
+        <v>122748554</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2054,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578923</v>
+        <v>578876</v>
       </c>
       <c r="R14" t="n">
-        <v>6428196</v>
+        <v>6428319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2127,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748554</v>
+        <v>122748650</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2165,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578876</v>
+        <v>578934</v>
       </c>
       <c r="R15" t="n">
-        <v>6428319</v>
+        <v>6428344</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748802</v>
+        <v>122748570</v>
       </c>
       <c r="B16" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,39 +2250,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2280,13 +2286,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578916</v>
+        <v>578855</v>
       </c>
       <c r="R16" t="n">
-        <v>6428228</v>
+        <v>6428305</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,6 +2330,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2342,7 +2349,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748824</v>
+        <v>122748608</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2390,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578919</v>
+        <v>578920</v>
       </c>
       <c r="R17" t="n">
-        <v>6428210</v>
+        <v>6428319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2460,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748474</v>
+        <v>122748871</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2501,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578871</v>
+        <v>578921</v>
       </c>
       <c r="R18" t="n">
-        <v>6428320</v>
+        <v>6428203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748669</v>
+        <v>122748824</v>
       </c>
       <c r="B19" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,38 +2583,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2615,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578951</v>
+        <v>578919</v>
       </c>
       <c r="R19" t="n">
-        <v>6428317</v>
+        <v>6428210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,7 +2682,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748710</v>
+        <v>122748974</v>
       </c>
       <c r="B20" t="n">
         <v>98355</v>
@@ -2726,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578908</v>
+        <v>578879</v>
       </c>
       <c r="R20" t="n">
-        <v>6428300</v>
+        <v>6428307</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2793,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748513</v>
+        <v>122748891</v>
       </c>
       <c r="B21" t="n">
         <v>98355</v>
@@ -2837,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578874</v>
+        <v>578919</v>
       </c>
       <c r="R21" t="n">
-        <v>6428309</v>
+        <v>6428209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,7 +2904,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748450</v>
+        <v>122748852</v>
       </c>
       <c r="B22" t="n">
         <v>98355</v>
@@ -2948,10 +2952,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578855</v>
+        <v>578925</v>
       </c>
       <c r="R22" t="n">
-        <v>6428306</v>
+        <v>6428192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3015,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748700</v>
+        <v>122748450</v>
       </c>
       <c r="B23" t="n">
         <v>98355</v>
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578948</v>
+        <v>578855</v>
       </c>
       <c r="R23" t="n">
-        <v>6428315</v>
+        <v>6428306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3126,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748939</v>
+        <v>122748530</v>
       </c>
       <c r="B24" t="n">
         <v>98355</v>
@@ -3170,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578966</v>
+        <v>578887</v>
       </c>
       <c r="R24" t="n">
-        <v>6428216</v>
+        <v>6428305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748770</v>
+        <v>122748939</v>
       </c>
       <c r="B25" t="n">
         <v>98355</v>
@@ -3281,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578907</v>
+        <v>578966</v>
       </c>
       <c r="R25" t="n">
-        <v>6428303</v>
+        <v>6428216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3348,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748974</v>
+        <v>122748922</v>
       </c>
       <c r="B26" t="n">
         <v>98355</v>
@@ -3388,14 +3392,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578879</v>
+        <v>578971</v>
       </c>
       <c r="R26" t="n">
-        <v>6428307</v>
+        <v>6428217</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,10 +3459,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748817</v>
+        <v>122748903</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,35 +3471,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3503,13 +3507,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578912</v>
+        <v>578994</v>
       </c>
       <c r="R27" t="n">
-        <v>6428250</v>
+        <v>6428205</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3547,6 +3551,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748749</v>
+        <v>122748838</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,35 +3582,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,13 +3622,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578854</v>
+        <v>578919</v>
       </c>
       <c r="R28" t="n">
-        <v>6428300</v>
+        <v>6428218</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3657,7 +3666,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3676,10 +3684,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748650</v>
+        <v>122748778</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>95126</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,33 +3696,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3724,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578934</v>
+        <v>578907</v>
       </c>
       <c r="R29" t="n">
-        <v>6428344</v>
+        <v>6428303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748608</v>
+        <v>122748749</v>
       </c>
       <c r="B30" t="n">
         <v>98355</v>
@@ -3835,10 +3839,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578920</v>
+        <v>578854</v>
       </c>
       <c r="R30" t="n">
-        <v>6428319</v>
+        <v>6428300</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,10 +3902,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748719</v>
+        <v>122748817</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>56688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,35 +3914,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3946,13 +3950,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578907</v>
+        <v>578912</v>
       </c>
       <c r="R31" t="n">
-        <v>6428320</v>
+        <v>6428250</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3990,7 +3994,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4009,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748838</v>
+        <v>122748878</v>
       </c>
       <c r="B32" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4021,39 +4024,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4061,13 +4060,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578919</v>
+        <v>578923</v>
       </c>
       <c r="R32" t="n">
-        <v>6428218</v>
+        <v>6428199</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4105,6 +4104,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748852</v>
+        <v>122748770</v>
       </c>
       <c r="B33" t="n">
         <v>98355</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578925</v>
+        <v>578907</v>
       </c>
       <c r="R33" t="n">
-        <v>6428192</v>
+        <v>6428303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832750</v>
+        <v>122832662</v>
       </c>
       <c r="B34" t="n">
         <v>98355</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578986</v>
+        <v>578900</v>
       </c>
       <c r="R34" t="n">
-        <v>6428201</v>
+        <v>6428250</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832101</v>
+        <v>122832077</v>
       </c>
       <c r="B35" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4357,29 +4357,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4389,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578875</v>
+        <v>578858</v>
       </c>
       <c r="R35" t="n">
-        <v>6428259</v>
+        <v>6428260</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4452,7 +4456,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832884</v>
+        <v>122832817</v>
       </c>
       <c r="B36" t="n">
         <v>98355</v>
@@ -4500,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578944</v>
+        <v>578996</v>
       </c>
       <c r="R36" t="n">
-        <v>6428183</v>
+        <v>6428222</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4563,7 +4567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832563</v>
+        <v>122832750</v>
       </c>
       <c r="B37" t="n">
         <v>98355</v>
@@ -4611,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578948</v>
+        <v>578986</v>
       </c>
       <c r="R37" t="n">
-        <v>6428141</v>
+        <v>6428201</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4674,7 +4678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832400</v>
+        <v>122832986</v>
       </c>
       <c r="B38" t="n">
         <v>98355</v>
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578935</v>
+        <v>578944</v>
       </c>
       <c r="R38" t="n">
-        <v>6428215</v>
+        <v>6428183</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4785,7 +4789,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832254</v>
+        <v>122831868</v>
       </c>
       <c r="B39" t="n">
         <v>98355</v>
@@ -4833,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578889</v>
+        <v>578848</v>
       </c>
       <c r="R39" t="n">
-        <v>6428248</v>
+        <v>6428302</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,7 +4900,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832592</v>
+        <v>122831927</v>
       </c>
       <c r="B40" t="n">
         <v>98355</v>
@@ -4944,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578925</v>
+        <v>578836</v>
       </c>
       <c r="R40" t="n">
-        <v>6428157</v>
+        <v>6428289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,7 +5011,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832675</v>
+        <v>122832456</v>
       </c>
       <c r="B41" t="n">
         <v>98355</v>
@@ -5055,10 +5059,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578924</v>
+        <v>578914</v>
       </c>
       <c r="R41" t="n">
-        <v>6428234</v>
+        <v>6428200</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,7 +5122,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832383</v>
+        <v>122832254</v>
       </c>
       <c r="B42" t="n">
         <v>98355</v>
@@ -5166,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578929</v>
+        <v>578889</v>
       </c>
       <c r="R42" t="n">
-        <v>6428202</v>
+        <v>6428248</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5229,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832436</v>
+        <v>122832768</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5241,39 +5245,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578943</v>
+        <v>578986</v>
       </c>
       <c r="R43" t="n">
-        <v>6428212</v>
+        <v>6428221</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5325,6 +5325,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5343,7 +5344,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832295</v>
+        <v>122832675</v>
       </c>
       <c r="B44" t="n">
         <v>98355</v>
@@ -5391,10 +5392,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578916</v>
+        <v>578924</v>
       </c>
       <c r="R44" t="n">
-        <v>6428220</v>
+        <v>6428234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832208</v>
+        <v>122832400</v>
       </c>
       <c r="B45" t="n">
         <v>98355</v>
@@ -5502,10 +5503,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578887</v>
+        <v>578935</v>
       </c>
       <c r="R45" t="n">
-        <v>6428260</v>
+        <v>6428215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5565,7 +5566,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832945</v>
+        <v>122832208</v>
       </c>
       <c r="B46" t="n">
         <v>98355</v>
@@ -5613,10 +5614,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578992</v>
+        <v>578887</v>
       </c>
       <c r="R46" t="n">
-        <v>6428165</v>
+        <v>6428260</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5676,7 +5677,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832686</v>
+        <v>122832730</v>
       </c>
       <c r="B47" t="n">
         <v>98355</v>
@@ -5727,7 +5728,7 @@
         <v>578971</v>
       </c>
       <c r="R47" t="n">
-        <v>6428232</v>
+        <v>6428216</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5787,7 +5788,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832231</v>
+        <v>122832157</v>
       </c>
       <c r="B48" t="n">
         <v>98355</v>
@@ -5835,10 +5836,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578889</v>
+        <v>578886</v>
       </c>
       <c r="R48" t="n">
-        <v>6428243</v>
+        <v>6428255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5898,7 +5899,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832768</v>
+        <v>122832846</v>
       </c>
       <c r="B49" t="n">
         <v>98355</v>
@@ -5946,10 +5947,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578986</v>
+        <v>578992</v>
       </c>
       <c r="R49" t="n">
-        <v>6428221</v>
+        <v>6428165</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6010,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832817</v>
+        <v>122832341</v>
       </c>
       <c r="B50" t="n">
         <v>98355</v>
@@ -6057,10 +6058,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578996</v>
+        <v>578917</v>
       </c>
       <c r="R50" t="n">
-        <v>6428222</v>
+        <v>6428212</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6120,7 +6121,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832784</v>
+        <v>122832231</v>
       </c>
       <c r="B51" t="n">
         <v>98355</v>
@@ -6168,10 +6169,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578994</v>
+        <v>578889</v>
       </c>
       <c r="R51" t="n">
-        <v>6428231</v>
+        <v>6428243</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6231,7 +6232,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832456</v>
+        <v>122832784</v>
       </c>
       <c r="B52" t="n">
         <v>98355</v>
@@ -6279,10 +6280,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578914</v>
+        <v>578994</v>
       </c>
       <c r="R52" t="n">
-        <v>6428200</v>
+        <v>6428231</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6342,10 +6343,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832341</v>
+        <v>122832101</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>95126</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6354,33 +6355,29 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6390,10 +6387,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578917</v>
+        <v>578875</v>
       </c>
       <c r="R53" t="n">
-        <v>6428212</v>
+        <v>6428259</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,7 +6450,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832702</v>
+        <v>122832563</v>
       </c>
       <c r="B54" t="n">
         <v>98355</v>
@@ -6501,10 +6498,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578972</v>
+        <v>578948</v>
       </c>
       <c r="R54" t="n">
-        <v>6428239</v>
+        <v>6428141</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6561,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832655</v>
+        <v>122832295</v>
       </c>
       <c r="B55" t="n">
         <v>98355</v>
@@ -6612,10 +6609,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578894</v>
+        <v>578916</v>
       </c>
       <c r="R55" t="n">
-        <v>6428171</v>
+        <v>6428220</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,7 +6672,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832730</v>
+        <v>122832686</v>
       </c>
       <c r="B56" t="n">
         <v>98355</v>
@@ -6726,7 +6723,7 @@
         <v>578971</v>
       </c>
       <c r="R56" t="n">
-        <v>6428216</v>
+        <v>6428232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6786,10 +6783,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122833108</v>
+        <v>122832530</v>
       </c>
       <c r="B57" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6798,39 +6795,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6838,13 +6831,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578912</v>
+        <v>578925</v>
       </c>
       <c r="R57" t="n">
-        <v>6428250</v>
+        <v>6428178</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6882,6 +6875,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6900,7 +6894,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832530</v>
+        <v>122832650</v>
       </c>
       <c r="B58" t="n">
         <v>98355</v>
@@ -6948,10 +6942,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578925</v>
+        <v>578917</v>
       </c>
       <c r="R58" t="n">
-        <v>6428178</v>
+        <v>6428142</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7011,10 +7005,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122831868</v>
+        <v>122833108</v>
       </c>
       <c r="B59" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7023,35 +7017,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7059,13 +7057,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578848</v>
+        <v>578912</v>
       </c>
       <c r="R59" t="n">
-        <v>6428302</v>
+        <v>6428250</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7103,7 +7101,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7122,10 +7119,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832077</v>
+        <v>122832436</v>
       </c>
       <c r="B60" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7134,35 +7131,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7170,13 +7171,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578858</v>
+        <v>578943</v>
       </c>
       <c r="R60" t="n">
-        <v>6428260</v>
+        <v>6428212</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7214,7 +7215,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832157</v>
+        <v>122832134</v>
       </c>
       <c r="B62" t="n">
         <v>98355</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578886</v>
+        <v>578881</v>
       </c>
       <c r="R62" t="n">
         <v>6428255</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832662</v>
+        <v>122832383</v>
       </c>
       <c r="B63" t="n">
         <v>98355</v>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578900</v>
+        <v>578929</v>
       </c>
       <c r="R63" t="n">
-        <v>6428250</v>
+        <v>6428202</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,7 +7566,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832134</v>
+        <v>122832702</v>
       </c>
       <c r="B64" t="n">
         <v>98355</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578881</v>
+        <v>578972</v>
       </c>
       <c r="R64" t="n">
-        <v>6428255</v>
+        <v>6428239</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832650</v>
+        <v>122832592</v>
       </c>
       <c r="B65" t="n">
         <v>98355</v>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578917</v>
+        <v>578925</v>
       </c>
       <c r="R65" t="n">
-        <v>6428142</v>
+        <v>6428157</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122831927</v>
+        <v>122832655</v>
       </c>
       <c r="B66" t="n">
         <v>98355</v>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578836</v>
+        <v>578894</v>
       </c>
       <c r="R66" t="n">
-        <v>6428289</v>
+        <v>6428171</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748625</v>
+        <v>122748778</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578926</v>
+        <v>578907</v>
       </c>
       <c r="R2" t="n">
-        <v>6428331</v>
+        <v>6428303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748710</v>
+        <v>122748878</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578908</v>
+        <v>578923</v>
       </c>
       <c r="R3" t="n">
-        <v>6428300</v>
+        <v>6428199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748669</v>
+        <v>122748903</v>
       </c>
       <c r="B4" t="n">
-        <v>91354</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +905,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578951</v>
+        <v>578994</v>
       </c>
       <c r="R4" t="n">
-        <v>6428317</v>
+        <v>6428205</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748719</v>
+        <v>122748700</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578907</v>
+        <v>578948</v>
       </c>
       <c r="R5" t="n">
-        <v>6428320</v>
+        <v>6428315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748692</v>
+        <v>122748650</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578948</v>
+        <v>578934</v>
       </c>
       <c r="R6" t="n">
-        <v>6428315</v>
+        <v>6428344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748865</v>
+        <v>122748491</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578923</v>
+        <v>578872</v>
       </c>
       <c r="R7" t="n">
-        <v>6428196</v>
+        <v>6428318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748491</v>
+        <v>122748749</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578872</v>
+        <v>578854</v>
       </c>
       <c r="R8" t="n">
-        <v>6428318</v>
+        <v>6428300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748474</v>
+        <v>122748824</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578871</v>
+        <v>578919</v>
       </c>
       <c r="R9" t="n">
-        <v>6428320</v>
+        <v>6428210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748802</v>
+        <v>122748852</v>
       </c>
       <c r="B10" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,39 +1571,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578916</v>
+        <v>578925</v>
       </c>
       <c r="R10" t="n">
-        <v>6428228</v>
+        <v>6428192</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,6 +1651,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748953</v>
+        <v>122748817</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,35 +1682,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578965</v>
+        <v>578912</v>
       </c>
       <c r="R11" t="n">
-        <v>6428213</v>
+        <v>6428250</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,7 +1762,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1791,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748513</v>
+        <v>122748891</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578874</v>
+        <v>578919</v>
       </c>
       <c r="R12" t="n">
-        <v>6428309</v>
+        <v>6428209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748796</v>
+        <v>122748802</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,37 +1903,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2016,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748554</v>
+        <v>122748974</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578876</v>
+        <v>578879</v>
       </c>
       <c r="R14" t="n">
-        <v>6428319</v>
+        <v>6428307</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748650</v>
+        <v>122748953</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578934</v>
+        <v>578965</v>
       </c>
       <c r="R15" t="n">
-        <v>6428344</v>
+        <v>6428213</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748570</v>
+        <v>122748865</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578855</v>
+        <v>578923</v>
       </c>
       <c r="R16" t="n">
-        <v>6428305</v>
+        <v>6428196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748608</v>
+        <v>122748770</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,10 +2386,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578920</v>
+        <v>578907</v>
       </c>
       <c r="R17" t="n">
-        <v>6428319</v>
+        <v>6428303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,10 +2449,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748871</v>
+        <v>122748450</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578921</v>
+        <v>578855</v>
       </c>
       <c r="R18" t="n">
-        <v>6428203</v>
+        <v>6428306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748824</v>
+        <v>122748719</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578919</v>
+        <v>578907</v>
       </c>
       <c r="R19" t="n">
-        <v>6428210</v>
+        <v>6428320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748974</v>
+        <v>122748570</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,10 +2719,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578879</v>
+        <v>578855</v>
       </c>
       <c r="R20" t="n">
-        <v>6428307</v>
+        <v>6428305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,10 +2782,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748891</v>
+        <v>122748838</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2805,35 +2794,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2844,10 +2837,10 @@
         <v>578919</v>
       </c>
       <c r="R21" t="n">
-        <v>6428209</v>
+        <v>6428218</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2878,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2904,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748852</v>
+        <v>122748871</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2952,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578925</v>
+        <v>578921</v>
       </c>
       <c r="R22" t="n">
-        <v>6428192</v>
+        <v>6428203</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748450</v>
+        <v>122748474</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578855</v>
+        <v>578871</v>
       </c>
       <c r="R23" t="n">
-        <v>6428306</v>
+        <v>6428320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3126,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748530</v>
+        <v>122748710</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,10 +3166,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578887</v>
+        <v>578908</v>
       </c>
       <c r="R24" t="n">
-        <v>6428305</v>
+        <v>6428300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748939</v>
+        <v>122748513</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,10 +3277,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578966</v>
+        <v>578874</v>
       </c>
       <c r="R25" t="n">
-        <v>6428216</v>
+        <v>6428309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,10 +3340,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748922</v>
+        <v>122748530</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,14 +3384,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578971</v>
+        <v>578887</v>
       </c>
       <c r="R26" t="n">
-        <v>6428217</v>
+        <v>6428305</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3459,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748903</v>
+        <v>122748669</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,35 +3463,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3507,10 +3502,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578994</v>
+        <v>578951</v>
       </c>
       <c r="R27" t="n">
-        <v>6428205</v>
+        <v>6428317</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748838</v>
+        <v>122748796</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3586,33 +3581,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3622,13 +3617,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578919</v>
+        <v>578916</v>
       </c>
       <c r="R28" t="n">
-        <v>6428218</v>
+        <v>6428228</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748778</v>
+        <v>122748922</v>
       </c>
       <c r="B29" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3696,42 +3691,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578907</v>
+        <v>578971</v>
       </c>
       <c r="R29" t="n">
-        <v>6428303</v>
+        <v>6428217</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3791,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748749</v>
+        <v>122748608</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,10 +3838,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578854</v>
+        <v>578920</v>
       </c>
       <c r="R30" t="n">
-        <v>6428300</v>
+        <v>6428319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3902,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748817</v>
+        <v>122748625</v>
       </c>
       <c r="B31" t="n">
-        <v>56688</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3914,35 +3913,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3950,13 +3949,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578912</v>
+        <v>578926</v>
       </c>
       <c r="R31" t="n">
-        <v>6428250</v>
+        <v>6428331</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3994,6 +3993,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748878</v>
+        <v>122748554</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578923</v>
+        <v>578876</v>
       </c>
       <c r="R32" t="n">
-        <v>6428199</v>
+        <v>6428319</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748770</v>
+        <v>122748939</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578907</v>
+        <v>578966</v>
       </c>
       <c r="R33" t="n">
-        <v>6428303</v>
+        <v>6428216</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832662</v>
+        <v>122832436</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4246,35 +4246,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4282,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578900</v>
+        <v>578943</v>
       </c>
       <c r="R34" t="n">
-        <v>6428250</v>
+        <v>6428212</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4330,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4345,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832077</v>
+        <v>122832550</v>
       </c>
       <c r="B35" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,10 +4396,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578858</v>
+        <v>578934</v>
       </c>
       <c r="R35" t="n">
-        <v>6428260</v>
+        <v>6428155</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832817</v>
+        <v>122832655</v>
       </c>
       <c r="B36" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578996</v>
+        <v>578894</v>
       </c>
       <c r="R36" t="n">
-        <v>6428222</v>
+        <v>6428171</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832750</v>
+        <v>122832784</v>
       </c>
       <c r="B37" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4615,10 +4618,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578986</v>
+        <v>578994</v>
       </c>
       <c r="R37" t="n">
-        <v>6428201</v>
+        <v>6428231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,10 +4681,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832986</v>
+        <v>122832675</v>
       </c>
       <c r="B38" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4726,10 +4729,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578944</v>
+        <v>578924</v>
       </c>
       <c r="R38" t="n">
-        <v>6428183</v>
+        <v>6428234</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122831868</v>
+        <v>122832101</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4801,33 +4804,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4837,10 +4836,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578848</v>
+        <v>578875</v>
       </c>
       <c r="R39" t="n">
-        <v>6428302</v>
+        <v>6428259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4900,10 +4899,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122831927</v>
+        <v>122832400</v>
       </c>
       <c r="B40" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,10 +4947,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578836</v>
+        <v>578935</v>
       </c>
       <c r="R40" t="n">
-        <v>6428289</v>
+        <v>6428215</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5011,10 +5010,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832456</v>
+        <v>122832986</v>
       </c>
       <c r="B41" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,10 +5058,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578914</v>
+        <v>578944</v>
       </c>
       <c r="R41" t="n">
-        <v>6428200</v>
+        <v>6428183</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5122,10 +5121,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832254</v>
+        <v>122832817</v>
       </c>
       <c r="B42" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5170,10 +5169,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578889</v>
+        <v>578996</v>
       </c>
       <c r="R42" t="n">
-        <v>6428248</v>
+        <v>6428222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,10 +5232,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832768</v>
+        <v>122832846</v>
       </c>
       <c r="B43" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5281,10 +5280,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578986</v>
+        <v>578992</v>
       </c>
       <c r="R43" t="n">
-        <v>6428221</v>
+        <v>6428165</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5344,10 +5343,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832675</v>
+        <v>122832077</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5392,10 +5391,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578924</v>
+        <v>578858</v>
       </c>
       <c r="R44" t="n">
-        <v>6428234</v>
+        <v>6428260</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,10 +5454,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832400</v>
+        <v>122832254</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,10 +5502,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578935</v>
+        <v>578889</v>
       </c>
       <c r="R45" t="n">
-        <v>6428215</v>
+        <v>6428248</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,10 +5565,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832208</v>
+        <v>122832768</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5614,10 +5613,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578887</v>
+        <v>578986</v>
       </c>
       <c r="R46" t="n">
-        <v>6428260</v>
+        <v>6428221</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832730</v>
+        <v>122832750</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5725,10 +5724,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578971</v>
+        <v>578986</v>
       </c>
       <c r="R47" t="n">
-        <v>6428216</v>
+        <v>6428201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832157</v>
+        <v>122831868</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5836,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578886</v>
+        <v>578848</v>
       </c>
       <c r="R48" t="n">
-        <v>6428255</v>
+        <v>6428302</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5899,10 +5898,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832846</v>
+        <v>122831927</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5947,10 +5946,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578992</v>
+        <v>578836</v>
       </c>
       <c r="R49" t="n">
-        <v>6428165</v>
+        <v>6428289</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6010,10 +6009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832341</v>
+        <v>122832456</v>
       </c>
       <c r="B50" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6058,10 +6057,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578917</v>
+        <v>578914</v>
       </c>
       <c r="R50" t="n">
-        <v>6428212</v>
+        <v>6428200</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,10 +6120,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832231</v>
+        <v>122832295</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578889</v>
+        <v>578916</v>
       </c>
       <c r="R51" t="n">
-        <v>6428243</v>
+        <v>6428220</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6232,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832784</v>
+        <v>122832231</v>
       </c>
       <c r="B52" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6280,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578994</v>
+        <v>578889</v>
       </c>
       <c r="R52" t="n">
-        <v>6428231</v>
+        <v>6428243</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6343,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832101</v>
+        <v>122832563</v>
       </c>
       <c r="B53" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6355,29 +6354,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6387,10 +6390,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578875</v>
+        <v>578948</v>
       </c>
       <c r="R53" t="n">
-        <v>6428259</v>
+        <v>6428141</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6450,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832563</v>
+        <v>122832650</v>
       </c>
       <c r="B54" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6498,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578948</v>
+        <v>578917</v>
       </c>
       <c r="R54" t="n">
-        <v>6428141</v>
+        <v>6428142</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6561,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832295</v>
+        <v>122832662</v>
       </c>
       <c r="B55" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6609,10 +6612,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578916</v>
+        <v>578900</v>
       </c>
       <c r="R55" t="n">
-        <v>6428220</v>
+        <v>6428250</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6672,10 +6675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832686</v>
+        <v>122832157</v>
       </c>
       <c r="B56" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6720,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578971</v>
+        <v>578886</v>
       </c>
       <c r="R56" t="n">
-        <v>6428232</v>
+        <v>6428255</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6783,10 +6786,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832530</v>
+        <v>122832702</v>
       </c>
       <c r="B57" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6831,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578925</v>
+        <v>578972</v>
       </c>
       <c r="R57" t="n">
-        <v>6428178</v>
+        <v>6428239</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6894,10 +6897,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832650</v>
+        <v>122832730</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6942,10 +6945,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578917</v>
+        <v>578971</v>
       </c>
       <c r="R58" t="n">
-        <v>6428142</v>
+        <v>6428216</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7005,10 +7008,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122833108</v>
+        <v>122832592</v>
       </c>
       <c r="B59" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7017,39 +7020,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7057,13 +7056,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578912</v>
+        <v>578925</v>
       </c>
       <c r="R59" t="n">
-        <v>6428250</v>
+        <v>6428157</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7101,6 +7100,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7119,10 +7119,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832436</v>
+        <v>122832341</v>
       </c>
       <c r="B60" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7131,39 +7131,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7171,13 +7167,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578943</v>
+        <v>578917</v>
       </c>
       <c r="R60" t="n">
         <v>6428212</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7215,6 +7211,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7233,10 +7230,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832550</v>
+        <v>122833108</v>
       </c>
       <c r="B61" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7245,35 +7242,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7281,13 +7282,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578934</v>
+        <v>578912</v>
       </c>
       <c r="R61" t="n">
-        <v>6428155</v>
+        <v>6428250</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7325,7 +7326,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832134</v>
+        <v>122832530</v>
       </c>
       <c r="B62" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578881</v>
+        <v>578925</v>
       </c>
       <c r="R62" t="n">
-        <v>6428255</v>
+        <v>6428178</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7455,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832383</v>
+        <v>122832686</v>
       </c>
       <c r="B63" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578929</v>
+        <v>578971</v>
       </c>
       <c r="R63" t="n">
-        <v>6428202</v>
+        <v>6428232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832702</v>
+        <v>122832208</v>
       </c>
       <c r="B64" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578972</v>
+        <v>578887</v>
       </c>
       <c r="R64" t="n">
-        <v>6428239</v>
+        <v>6428260</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832592</v>
+        <v>122832383</v>
       </c>
       <c r="B65" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578925</v>
+        <v>578929</v>
       </c>
       <c r="R65" t="n">
-        <v>6428157</v>
+        <v>6428202</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832655</v>
+        <v>122832134</v>
       </c>
       <c r="B66" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578894</v>
+        <v>578881</v>
       </c>
       <c r="R66" t="n">
-        <v>6428171</v>
+        <v>6428255</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -3565,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748796</v>
+        <v>122748922</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,53 +3577,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578916</v>
+        <v>578971</v>
       </c>
       <c r="R28" t="n">
-        <v>6428228</v>
+        <v>6428217</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,6 +3657,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3679,7 +3676,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748922</v>
+        <v>122748608</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3723,14 +3720,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578971</v>
+        <v>578920</v>
       </c>
       <c r="R29" t="n">
-        <v>6428217</v>
+        <v>6428319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748608</v>
+        <v>122748796</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3802,35 +3799,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3838,13 +3839,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578920</v>
+        <v>578916</v>
       </c>
       <c r="R30" t="n">
-        <v>6428319</v>
+        <v>6428228</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3882,7 +3883,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -3565,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748922</v>
+        <v>122748796</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,49 +3577,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578971</v>
+        <v>578916</v>
       </c>
       <c r="R28" t="n">
-        <v>6428217</v>
+        <v>6428228</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3657,7 +3661,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3676,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748608</v>
+        <v>122748922</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3720,14 +3723,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578920</v>
+        <v>578971</v>
       </c>
       <c r="R29" t="n">
-        <v>6428319</v>
+        <v>6428217</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748796</v>
+        <v>122748608</v>
       </c>
       <c r="B30" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3799,39 +3802,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3839,13 +3838,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578916</v>
+        <v>578920</v>
       </c>
       <c r="R30" t="n">
-        <v>6428228</v>
+        <v>6428319</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3883,6 +3882,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748778</v>
+        <v>122748838</v>
       </c>
       <c r="B2" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578907</v>
+        <v>578919</v>
       </c>
       <c r="R2" t="n">
-        <v>6428303</v>
+        <v>6428218</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748878</v>
+        <v>122748891</v>
       </c>
       <c r="B3" t="n">
         <v>98357</v>
@@ -830,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578923</v>
+        <v>578919</v>
       </c>
       <c r="R3" t="n">
-        <v>6428199</v>
+        <v>6428209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748903</v>
+        <v>122748491</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -941,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578994</v>
+        <v>578872</v>
       </c>
       <c r="R4" t="n">
-        <v>6428205</v>
+        <v>6428318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748700</v>
+        <v>122748817</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578948</v>
+        <v>578912</v>
       </c>
       <c r="R5" t="n">
-        <v>6428315</v>
+        <v>6428250</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1103,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748650</v>
+        <v>122748474</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1163,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578934</v>
+        <v>578871</v>
       </c>
       <c r="R6" t="n">
-        <v>6428344</v>
+        <v>6428320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748491</v>
+        <v>122748903</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1274,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578872</v>
+        <v>578994</v>
       </c>
       <c r="R7" t="n">
-        <v>6428318</v>
+        <v>6428205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748749</v>
+        <v>122748692</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1385,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578854</v>
+        <v>578948</v>
       </c>
       <c r="R8" t="n">
-        <v>6428300</v>
+        <v>6428315</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748824</v>
+        <v>122748637</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1496,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578919</v>
+        <v>578855</v>
       </c>
       <c r="R9" t="n">
-        <v>6428210</v>
+        <v>6428305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748852</v>
+        <v>122748554</v>
       </c>
       <c r="B10" t="n">
         <v>98357</v>
@@ -1607,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578925</v>
+        <v>578876</v>
       </c>
       <c r="R10" t="n">
-        <v>6428192</v>
+        <v>6428319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748817</v>
+        <v>122748802</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>57848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,29 +1692,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1718,13 +1728,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578912</v>
+        <v>578916</v>
       </c>
       <c r="R11" t="n">
-        <v>6428250</v>
+        <v>6428228</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748891</v>
+        <v>122748778</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,33 +1802,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1828,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578919</v>
+        <v>578907</v>
       </c>
       <c r="R12" t="n">
-        <v>6428209</v>
+        <v>6428303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748802</v>
+        <v>122748974</v>
       </c>
       <c r="B13" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,39 +1909,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,13 +1945,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578916</v>
+        <v>578879</v>
       </c>
       <c r="R13" t="n">
-        <v>6428228</v>
+        <v>6428307</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,6 +1989,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,7 +2008,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748974</v>
+        <v>122748513</v>
       </c>
       <c r="B14" t="n">
         <v>98357</v>
@@ -2053,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578879</v>
+        <v>578874</v>
       </c>
       <c r="R14" t="n">
-        <v>6428307</v>
+        <v>6428309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2119,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748953</v>
+        <v>122748749</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2164,10 +2167,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578965</v>
+        <v>578854</v>
       </c>
       <c r="R15" t="n">
-        <v>6428213</v>
+        <v>6428300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2230,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748865</v>
+        <v>122748939</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2275,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578923</v>
+        <v>578966</v>
       </c>
       <c r="R16" t="n">
-        <v>6428196</v>
+        <v>6428216</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2341,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748770</v>
+        <v>122748625</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2386,10 +2389,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578907</v>
+        <v>578926</v>
       </c>
       <c r="R17" t="n">
-        <v>6428303</v>
+        <v>6428331</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2449,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748450</v>
+        <v>122748796</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,35 +2464,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2497,13 +2504,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578855</v>
+        <v>578916</v>
       </c>
       <c r="R18" t="n">
-        <v>6428306</v>
+        <v>6428228</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2541,7 +2548,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2560,7 +2566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748719</v>
+        <v>122748770</v>
       </c>
       <c r="B19" t="n">
         <v>98357</v>
@@ -2611,7 +2617,7 @@
         <v>578907</v>
       </c>
       <c r="R19" t="n">
-        <v>6428320</v>
+        <v>6428303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2677,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748570</v>
+        <v>122748530</v>
       </c>
       <c r="B20" t="n">
         <v>98357</v>
@@ -2719,7 +2725,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578855</v>
+        <v>578887</v>
       </c>
       <c r="R20" t="n">
         <v>6428305</v>
@@ -2782,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748838</v>
+        <v>122748710</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2794,39 +2800,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2834,13 +2836,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578919</v>
+        <v>578908</v>
       </c>
       <c r="R21" t="n">
-        <v>6428218</v>
+        <v>6428300</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,6 +2880,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3007,7 +3010,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748474</v>
+        <v>122748865</v>
       </c>
       <c r="B23" t="n">
         <v>98357</v>
@@ -3055,10 +3058,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578871</v>
+        <v>578923</v>
       </c>
       <c r="R23" t="n">
-        <v>6428320</v>
+        <v>6428196</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748710</v>
+        <v>122748669</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>91354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,35 +3133,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3166,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578908</v>
+        <v>578951</v>
       </c>
       <c r="R24" t="n">
-        <v>6428300</v>
+        <v>6428317</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3235,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748513</v>
+        <v>122748450</v>
       </c>
       <c r="B25" t="n">
         <v>98357</v>
@@ -3277,10 +3283,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578874</v>
+        <v>578855</v>
       </c>
       <c r="R25" t="n">
-        <v>6428309</v>
+        <v>6428306</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3346,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748530</v>
+        <v>122748953</v>
       </c>
       <c r="B26" t="n">
         <v>98357</v>
@@ -3388,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578887</v>
+        <v>578965</v>
       </c>
       <c r="R26" t="n">
-        <v>6428305</v>
+        <v>6428213</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,10 +3457,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748669</v>
+        <v>122748852</v>
       </c>
       <c r="B27" t="n">
-        <v>91354</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3463,38 +3469,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3502,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578951</v>
+        <v>578925</v>
       </c>
       <c r="R27" t="n">
-        <v>6428317</v>
+        <v>6428192</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,10 +3568,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748796</v>
+        <v>122748922</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,53 +3580,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578916</v>
+        <v>578971</v>
       </c>
       <c r="R28" t="n">
-        <v>6428228</v>
+        <v>6428217</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,6 +3660,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748922</v>
+        <v>122748824</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3723,14 +3723,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578971</v>
+        <v>578919</v>
       </c>
       <c r="R29" t="n">
-        <v>6428217</v>
+        <v>6428210</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748625</v>
+        <v>122748719</v>
       </c>
       <c r="B31" t="n">
         <v>98357</v>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578926</v>
+        <v>578907</v>
       </c>
       <c r="R31" t="n">
-        <v>6428331</v>
+        <v>6428320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748554</v>
+        <v>122748878</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578876</v>
+        <v>578923</v>
       </c>
       <c r="R32" t="n">
-        <v>6428319</v>
+        <v>6428199</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748939</v>
+        <v>122748650</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578966</v>
+        <v>578934</v>
       </c>
       <c r="R33" t="n">
-        <v>6428216</v>
+        <v>6428344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832436</v>
+        <v>122832341</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4246,39 +4246,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4286,13 +4282,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578943</v>
+        <v>578917</v>
       </c>
       <c r="R34" t="n">
         <v>6428212</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4330,6 +4326,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4348,7 +4345,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832550</v>
+        <v>122832686</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4396,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578934</v>
+        <v>578971</v>
       </c>
       <c r="R35" t="n">
-        <v>6428155</v>
+        <v>6428232</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,7 +4456,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832655</v>
+        <v>122832750</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4507,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578894</v>
+        <v>578986</v>
       </c>
       <c r="R36" t="n">
-        <v>6428171</v>
+        <v>6428201</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,7 +4567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832784</v>
+        <v>122831927</v>
       </c>
       <c r="B37" t="n">
         <v>98357</v>
@@ -4618,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578994</v>
+        <v>578836</v>
       </c>
       <c r="R37" t="n">
-        <v>6428231</v>
+        <v>6428289</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,10 +4678,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832675</v>
+        <v>122833108</v>
       </c>
       <c r="B38" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4693,35 +4690,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4729,13 +4730,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578924</v>
+        <v>578912</v>
       </c>
       <c r="R38" t="n">
-        <v>6428234</v>
+        <v>6428250</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4773,7 +4774,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832101</v>
+        <v>122831868</v>
       </c>
       <c r="B39" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4804,29 +4804,33 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4836,10 +4840,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578875</v>
+        <v>578848</v>
       </c>
       <c r="R39" t="n">
-        <v>6428259</v>
+        <v>6428302</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4899,7 +4903,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832400</v>
+        <v>122832208</v>
       </c>
       <c r="B40" t="n">
         <v>98357</v>
@@ -4947,10 +4951,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578935</v>
+        <v>578887</v>
       </c>
       <c r="R40" t="n">
-        <v>6428215</v>
+        <v>6428260</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5010,7 +5014,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832986</v>
+        <v>122832945</v>
       </c>
       <c r="B41" t="n">
         <v>98357</v>
@@ -5058,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578944</v>
+        <v>578992</v>
       </c>
       <c r="R41" t="n">
-        <v>6428183</v>
+        <v>6428165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5121,7 +5125,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832817</v>
+        <v>122832884</v>
       </c>
       <c r="B42" t="n">
         <v>98357</v>
@@ -5169,10 +5173,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578996</v>
+        <v>578944</v>
       </c>
       <c r="R42" t="n">
-        <v>6428222</v>
+        <v>6428183</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5232,7 +5236,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832846</v>
+        <v>122832383</v>
       </c>
       <c r="B43" t="n">
         <v>98357</v>
@@ -5280,10 +5284,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578992</v>
+        <v>578929</v>
       </c>
       <c r="R43" t="n">
-        <v>6428165</v>
+        <v>6428202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5343,10 +5347,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832077</v>
+        <v>122832101</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5355,33 +5359,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578858</v>
+        <v>578875</v>
       </c>
       <c r="R44" t="n">
-        <v>6428260</v>
+        <v>6428259</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832254</v>
+        <v>122832675</v>
       </c>
       <c r="B45" t="n">
         <v>98357</v>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578889</v>
+        <v>578924</v>
       </c>
       <c r="R45" t="n">
-        <v>6428248</v>
+        <v>6428234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832768</v>
+        <v>122832400</v>
       </c>
       <c r="B46" t="n">
         <v>98357</v>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578986</v>
+        <v>578935</v>
       </c>
       <c r="R46" t="n">
-        <v>6428221</v>
+        <v>6428215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832750</v>
+        <v>122832730</v>
       </c>
       <c r="B47" t="n">
         <v>98357</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578986</v>
+        <v>578971</v>
       </c>
       <c r="R47" t="n">
-        <v>6428201</v>
+        <v>6428216</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5787,7 +5787,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122831868</v>
+        <v>122832817</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578848</v>
+        <v>578996</v>
       </c>
       <c r="R48" t="n">
-        <v>6428302</v>
+        <v>6428222</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122831927</v>
+        <v>122832655</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578836</v>
+        <v>578894</v>
       </c>
       <c r="R49" t="n">
-        <v>6428289</v>
+        <v>6428171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832456</v>
+        <v>122832231</v>
       </c>
       <c r="B50" t="n">
         <v>98357</v>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578914</v>
+        <v>578889</v>
       </c>
       <c r="R50" t="n">
-        <v>6428200</v>
+        <v>6428243</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832295</v>
+        <v>122832134</v>
       </c>
       <c r="B51" t="n">
         <v>98357</v>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578916</v>
+        <v>578881</v>
       </c>
       <c r="R51" t="n">
-        <v>6428220</v>
+        <v>6428255</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832231</v>
+        <v>122832077</v>
       </c>
       <c r="B52" t="n">
         <v>98357</v>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578889</v>
+        <v>578858</v>
       </c>
       <c r="R52" t="n">
-        <v>6428243</v>
+        <v>6428260</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6342,7 +6342,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832563</v>
+        <v>122832650</v>
       </c>
       <c r="B53" t="n">
         <v>98357</v>
@@ -6390,10 +6390,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578948</v>
+        <v>578917</v>
       </c>
       <c r="R53" t="n">
-        <v>6428141</v>
+        <v>6428142</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832650</v>
+        <v>122832592</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578917</v>
+        <v>578925</v>
       </c>
       <c r="R54" t="n">
-        <v>6428142</v>
+        <v>6428157</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832662</v>
+        <v>122832563</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578900</v>
+        <v>578948</v>
       </c>
       <c r="R55" t="n">
-        <v>6428250</v>
+        <v>6428141</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832157</v>
+        <v>122832784</v>
       </c>
       <c r="B56" t="n">
         <v>98357</v>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578886</v>
+        <v>578994</v>
       </c>
       <c r="R56" t="n">
-        <v>6428255</v>
+        <v>6428231</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832702</v>
+        <v>122832254</v>
       </c>
       <c r="B57" t="n">
         <v>98357</v>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578972</v>
+        <v>578889</v>
       </c>
       <c r="R57" t="n">
-        <v>6428239</v>
+        <v>6428248</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832730</v>
+        <v>122832436</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6909,35 +6909,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6945,13 +6949,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578971</v>
+        <v>578943</v>
       </c>
       <c r="R58" t="n">
-        <v>6428216</v>
+        <v>6428212</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6989,7 +6993,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7008,7 +7011,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832592</v>
+        <v>122832662</v>
       </c>
       <c r="B59" t="n">
         <v>98357</v>
@@ -7056,10 +7059,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578925</v>
+        <v>578900</v>
       </c>
       <c r="R59" t="n">
-        <v>6428157</v>
+        <v>6428250</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7119,7 +7122,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832341</v>
+        <v>122832550</v>
       </c>
       <c r="B60" t="n">
         <v>98357</v>
@@ -7167,10 +7170,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578917</v>
+        <v>578934</v>
       </c>
       <c r="R60" t="n">
-        <v>6428212</v>
+        <v>6428155</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7230,10 +7233,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122833108</v>
+        <v>122832157</v>
       </c>
       <c r="B61" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7242,39 +7245,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7282,13 +7281,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578912</v>
+        <v>578886</v>
       </c>
       <c r="R61" t="n">
-        <v>6428250</v>
+        <v>6428255</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7326,6 +7325,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832530</v>
+        <v>122832768</v>
       </c>
       <c r="B62" t="n">
         <v>98357</v>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578925</v>
+        <v>578986</v>
       </c>
       <c r="R62" t="n">
-        <v>6428178</v>
+        <v>6428221</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832686</v>
+        <v>122832295</v>
       </c>
       <c r="B63" t="n">
         <v>98357</v>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578971</v>
+        <v>578916</v>
       </c>
       <c r="R63" t="n">
-        <v>6428232</v>
+        <v>6428220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,7 +7566,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832208</v>
+        <v>122832530</v>
       </c>
       <c r="B64" t="n">
         <v>98357</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578887</v>
+        <v>578925</v>
       </c>
       <c r="R64" t="n">
-        <v>6428260</v>
+        <v>6428178</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832383</v>
+        <v>122832456</v>
       </c>
       <c r="B65" t="n">
         <v>98357</v>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578929</v>
+        <v>578914</v>
       </c>
       <c r="R65" t="n">
-        <v>6428202</v>
+        <v>6428200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832134</v>
+        <v>122832702</v>
       </c>
       <c r="B66" t="n">
         <v>98357</v>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578881</v>
+        <v>578972</v>
       </c>
       <c r="R66" t="n">
-        <v>6428255</v>
+        <v>6428239</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748838</v>
+        <v>122748570</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578919</v>
+        <v>578855</v>
       </c>
       <c r="R2" t="n">
-        <v>6428218</v>
+        <v>6428305</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748891</v>
+        <v>122748939</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578919</v>
+        <v>578966</v>
       </c>
       <c r="R3" t="n">
-        <v>6428209</v>
+        <v>6428216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748491</v>
+        <v>122748953</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578872</v>
+        <v>578965</v>
       </c>
       <c r="R4" t="n">
-        <v>6428318</v>
+        <v>6428213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748817</v>
+        <v>122748710</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578912</v>
+        <v>578908</v>
       </c>
       <c r="R5" t="n">
-        <v>6428250</v>
+        <v>6428300</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,6 +1100,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748474</v>
+        <v>122748700</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578871</v>
+        <v>578948</v>
       </c>
       <c r="R6" t="n">
-        <v>6428320</v>
+        <v>6428315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1233,7 @@
         <v>122748903</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748692</v>
+        <v>122748802</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,35 +1353,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578948</v>
+        <v>578916</v>
       </c>
       <c r="R8" t="n">
-        <v>6428315</v>
+        <v>6428228</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1437,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748637</v>
+        <v>122748770</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578855</v>
+        <v>578907</v>
       </c>
       <c r="R9" t="n">
-        <v>6428305</v>
+        <v>6428303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748554</v>
+        <v>122748852</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578876</v>
+        <v>578925</v>
       </c>
       <c r="R10" t="n">
-        <v>6428319</v>
+        <v>6428192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748802</v>
+        <v>122748608</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,39 +1689,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,13 +1725,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578916</v>
+        <v>578920</v>
       </c>
       <c r="R11" t="n">
-        <v>6428228</v>
+        <v>6428319</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,6 +1769,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1790,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748778</v>
+        <v>122748878</v>
       </c>
       <c r="B12" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,29 +1800,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1834,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578907</v>
+        <v>578923</v>
       </c>
       <c r="R12" t="n">
-        <v>6428303</v>
+        <v>6428199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748974</v>
+        <v>122748838</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,35 +1911,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1945,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578879</v>
+        <v>578919</v>
       </c>
       <c r="R13" t="n">
-        <v>6428307</v>
+        <v>6428218</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2008,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748513</v>
+        <v>122748778</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,33 +2025,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2056,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578874</v>
+        <v>578907</v>
       </c>
       <c r="R14" t="n">
-        <v>6428309</v>
+        <v>6428303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748749</v>
+        <v>122748625</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578854</v>
+        <v>578926</v>
       </c>
       <c r="R15" t="n">
-        <v>6428300</v>
+        <v>6428331</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748939</v>
+        <v>122748513</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578966</v>
+        <v>578874</v>
       </c>
       <c r="R16" t="n">
-        <v>6428216</v>
+        <v>6428309</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748625</v>
+        <v>122748865</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578926</v>
+        <v>578923</v>
       </c>
       <c r="R17" t="n">
-        <v>6428331</v>
+        <v>6428196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748796</v>
+        <v>122748650</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,39 +2465,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2504,13 +2501,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578916</v>
+        <v>578934</v>
       </c>
       <c r="R18" t="n">
-        <v>6428228</v>
+        <v>6428344</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,6 +2545,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2566,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748770</v>
+        <v>122748891</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2614,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578907</v>
+        <v>578919</v>
       </c>
       <c r="R19" t="n">
-        <v>6428303</v>
+        <v>6428209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,7 +2678,7 @@
         <v>122748530</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2788,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748710</v>
+        <v>122748554</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,10 +2834,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578908</v>
+        <v>578876</v>
       </c>
       <c r="R21" t="n">
-        <v>6428300</v>
+        <v>6428319</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748871</v>
+        <v>122748922</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,14 +2941,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578921</v>
+        <v>578971</v>
       </c>
       <c r="R22" t="n">
-        <v>6428203</v>
+        <v>6428217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748865</v>
+        <v>122748450</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,10 +3056,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578923</v>
+        <v>578855</v>
       </c>
       <c r="R23" t="n">
-        <v>6428196</v>
+        <v>6428306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748669</v>
+        <v>122748871</v>
       </c>
       <c r="B24" t="n">
-        <v>91354</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,38 +3131,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3172,10 +3167,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578951</v>
+        <v>578921</v>
       </c>
       <c r="R24" t="n">
-        <v>6428317</v>
+        <v>6428203</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748450</v>
+        <v>122748669</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>91362</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3247,35 +3242,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3283,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578855</v>
+        <v>578951</v>
       </c>
       <c r="R25" t="n">
-        <v>6428306</v>
+        <v>6428317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748953</v>
+        <v>122748719</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578965</v>
+        <v>578907</v>
       </c>
       <c r="R26" t="n">
-        <v>6428213</v>
+        <v>6428320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748852</v>
+        <v>122748817</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3469,35 +3467,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3505,13 +3503,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578925</v>
+        <v>578912</v>
       </c>
       <c r="R27" t="n">
-        <v>6428192</v>
+        <v>6428250</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3549,7 +3547,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3568,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748922</v>
+        <v>122748796</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3580,49 +3577,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578971</v>
+        <v>578916</v>
       </c>
       <c r="R28" t="n">
-        <v>6428217</v>
+        <v>6428228</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3660,7 +3661,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748824</v>
+        <v>122748974</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578919</v>
+        <v>578879</v>
       </c>
       <c r="R29" t="n">
-        <v>6428210</v>
+        <v>6428307</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748608</v>
+        <v>122748474</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578920</v>
+        <v>578871</v>
       </c>
       <c r="R30" t="n">
-        <v>6428319</v>
+        <v>6428320</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748719</v>
+        <v>122748749</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578907</v>
+        <v>578854</v>
       </c>
       <c r="R31" t="n">
-        <v>6428320</v>
+        <v>6428300</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748878</v>
+        <v>122748824</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578923</v>
+        <v>578919</v>
       </c>
       <c r="R32" t="n">
-        <v>6428199</v>
+        <v>6428210</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748650</v>
+        <v>122748491</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578934</v>
+        <v>578872</v>
       </c>
       <c r="R33" t="n">
-        <v>6428344</v>
+        <v>6428318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832341</v>
+        <v>122832101</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4246,33 +4246,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4282,10 +4278,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578917</v>
+        <v>578875</v>
       </c>
       <c r="R34" t="n">
-        <v>6428212</v>
+        <v>6428259</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4341,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832686</v>
+        <v>122832341</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,10 +4389,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578971</v>
+        <v>578917</v>
       </c>
       <c r="R35" t="n">
-        <v>6428232</v>
+        <v>6428212</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,10 +4452,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832750</v>
+        <v>122832295</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,10 +4500,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578986</v>
+        <v>578916</v>
       </c>
       <c r="R36" t="n">
-        <v>6428201</v>
+        <v>6428220</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,10 +4563,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122831927</v>
+        <v>122832254</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4615,10 +4611,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578836</v>
+        <v>578889</v>
       </c>
       <c r="R37" t="n">
-        <v>6428289</v>
+        <v>6428248</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,10 +4674,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122833108</v>
+        <v>122832157</v>
       </c>
       <c r="B38" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4690,39 +4686,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4730,13 +4722,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578912</v>
+        <v>578886</v>
       </c>
       <c r="R38" t="n">
-        <v>6428250</v>
+        <v>6428255</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4774,6 +4766,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4785,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122831868</v>
+        <v>122832884</v>
       </c>
       <c r="B39" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4840,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578848</v>
+        <v>578944</v>
       </c>
       <c r="R39" t="n">
-        <v>6428302</v>
+        <v>6428183</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4903,10 +4896,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832208</v>
+        <v>122832702</v>
       </c>
       <c r="B40" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4951,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578887</v>
+        <v>578972</v>
       </c>
       <c r="R40" t="n">
-        <v>6428260</v>
+        <v>6428239</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5014,10 +5007,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832945</v>
+        <v>122832846</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5125,10 +5118,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832884</v>
+        <v>122832768</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5173,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578944</v>
+        <v>578986</v>
       </c>
       <c r="R42" t="n">
-        <v>6428183</v>
+        <v>6428221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5236,10 +5229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832383</v>
+        <v>122832231</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5284,10 +5277,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578929</v>
+        <v>578889</v>
       </c>
       <c r="R43" t="n">
-        <v>6428202</v>
+        <v>6428243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5347,10 +5340,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832101</v>
+        <v>122832436</v>
       </c>
       <c r="B44" t="n">
-        <v>95128</v>
+        <v>57631</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5359,31 +5352,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5391,13 +5392,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578875</v>
+        <v>578943</v>
       </c>
       <c r="R44" t="n">
-        <v>6428259</v>
+        <v>6428212</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5435,7 +5436,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5454,10 +5454,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832675</v>
+        <v>122832662</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578924</v>
+        <v>578900</v>
       </c>
       <c r="R45" t="n">
-        <v>6428234</v>
+        <v>6428250</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
         <v>122832400</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5676,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832730</v>
+        <v>122832456</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578971</v>
+        <v>578914</v>
       </c>
       <c r="R47" t="n">
-        <v>6428216</v>
+        <v>6428200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832817</v>
+        <v>122832784</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578996</v>
+        <v>578994</v>
       </c>
       <c r="R48" t="n">
-        <v>6428222</v>
+        <v>6428231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832655</v>
+        <v>122832077</v>
       </c>
       <c r="B49" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578894</v>
+        <v>578858</v>
       </c>
       <c r="R49" t="n">
-        <v>6428171</v>
+        <v>6428260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,10 +6009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832231</v>
+        <v>122831927</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578889</v>
+        <v>578836</v>
       </c>
       <c r="R50" t="n">
-        <v>6428243</v>
+        <v>6428289</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832134</v>
+        <v>122832730</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578881</v>
+        <v>578971</v>
       </c>
       <c r="R51" t="n">
-        <v>6428255</v>
+        <v>6428216</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6231,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832077</v>
+        <v>122832134</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578858</v>
+        <v>578881</v>
       </c>
       <c r="R52" t="n">
-        <v>6428260</v>
+        <v>6428255</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832650</v>
+        <v>122832655</v>
       </c>
       <c r="B53" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6390,10 +6390,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578917</v>
+        <v>578894</v>
       </c>
       <c r="R53" t="n">
-        <v>6428142</v>
+        <v>6428171</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832592</v>
+        <v>122831868</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578925</v>
+        <v>578848</v>
       </c>
       <c r="R54" t="n">
-        <v>6428157</v>
+        <v>6428302</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>122832563</v>
       </c>
       <c r="B55" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832784</v>
+        <v>122832383</v>
       </c>
       <c r="B56" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578994</v>
+        <v>578929</v>
       </c>
       <c r="R56" t="n">
-        <v>6428231</v>
+        <v>6428202</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832254</v>
+        <v>122832592</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578889</v>
+        <v>578925</v>
       </c>
       <c r="R57" t="n">
-        <v>6428248</v>
+        <v>6428157</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832436</v>
+        <v>122833108</v>
       </c>
       <c r="B58" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6909,37 +6909,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578943</v>
+        <v>578912</v>
       </c>
       <c r="R58" t="n">
-        <v>6428212</v>
+        <v>6428250</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832662</v>
+        <v>122832686</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578900</v>
+        <v>578971</v>
       </c>
       <c r="R59" t="n">
-        <v>6428250</v>
+        <v>6428232</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832550</v>
+        <v>122832817</v>
       </c>
       <c r="B60" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578934</v>
+        <v>578996</v>
       </c>
       <c r="R60" t="n">
-        <v>6428155</v>
+        <v>6428222</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832157</v>
+        <v>122832750</v>
       </c>
       <c r="B61" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578886</v>
+        <v>578986</v>
       </c>
       <c r="R61" t="n">
-        <v>6428255</v>
+        <v>6428201</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832768</v>
+        <v>122832530</v>
       </c>
       <c r="B62" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578986</v>
+        <v>578925</v>
       </c>
       <c r="R62" t="n">
-        <v>6428221</v>
+        <v>6428178</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7455,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832295</v>
+        <v>122832675</v>
       </c>
       <c r="B63" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578916</v>
+        <v>578924</v>
       </c>
       <c r="R63" t="n">
-        <v>6428220</v>
+        <v>6428234</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832530</v>
+        <v>122832208</v>
       </c>
       <c r="B64" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578925</v>
+        <v>578887</v>
       </c>
       <c r="R64" t="n">
-        <v>6428178</v>
+        <v>6428260</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832456</v>
+        <v>122832550</v>
       </c>
       <c r="B65" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578914</v>
+        <v>578934</v>
       </c>
       <c r="R65" t="n">
-        <v>6428200</v>
+        <v>6428155</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832702</v>
+        <v>122832650</v>
       </c>
       <c r="B66" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578972</v>
+        <v>578917</v>
       </c>
       <c r="R66" t="n">
-        <v>6428239</v>
+        <v>6428142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -6120,7 +6120,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832730</v>
+        <v>122832134</v>
       </c>
       <c r="B51" t="n">
         <v>98365</v>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578971</v>
+        <v>578881</v>
       </c>
       <c r="R51" t="n">
-        <v>6428216</v>
+        <v>6428255</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832134</v>
+        <v>122832730</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578881</v>
+        <v>578971</v>
       </c>
       <c r="R52" t="n">
-        <v>6428255</v>
+        <v>6428216</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832550</v>
+        <v>122832650</v>
       </c>
       <c r="B65" t="n">
         <v>98365</v>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578934</v>
+        <v>578917</v>
       </c>
       <c r="R65" t="n">
-        <v>6428155</v>
+        <v>6428142</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832650</v>
+        <v>122832550</v>
       </c>
       <c r="B66" t="n">
         <v>98365</v>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578917</v>
+        <v>578934</v>
       </c>
       <c r="R66" t="n">
-        <v>6428142</v>
+        <v>6428155</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748570</v>
+        <v>122748710</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578855</v>
+        <v>578908</v>
       </c>
       <c r="R2" t="n">
-        <v>6428305</v>
+        <v>6428300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748939</v>
+        <v>122748953</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578966</v>
+        <v>578965</v>
       </c>
       <c r="R3" t="n">
-        <v>6428216</v>
+        <v>6428213</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748953</v>
+        <v>122748450</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578965</v>
+        <v>578855</v>
       </c>
       <c r="R4" t="n">
-        <v>6428213</v>
+        <v>6428306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748710</v>
+        <v>122748891</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578908</v>
+        <v>578919</v>
       </c>
       <c r="R5" t="n">
-        <v>6428300</v>
+        <v>6428209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748700</v>
+        <v>122748554</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578948</v>
+        <v>578876</v>
       </c>
       <c r="R6" t="n">
-        <v>6428315</v>
+        <v>6428319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748903</v>
+        <v>122748865</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578994</v>
+        <v>578923</v>
       </c>
       <c r="R7" t="n">
-        <v>6428205</v>
+        <v>6428196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748802</v>
+        <v>122748939</v>
       </c>
       <c r="B8" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1353,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1389,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578916</v>
+        <v>578966</v>
       </c>
       <c r="R8" t="n">
-        <v>6428228</v>
+        <v>6428216</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748770</v>
+        <v>122748922</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1499,14 +1496,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578907</v>
+        <v>578971</v>
       </c>
       <c r="R9" t="n">
-        <v>6428303</v>
+        <v>6428217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748852</v>
+        <v>122748871</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578925</v>
+        <v>578921</v>
       </c>
       <c r="R10" t="n">
-        <v>6428192</v>
+        <v>6428203</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748608</v>
+        <v>122748530</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578920</v>
+        <v>578887</v>
       </c>
       <c r="R11" t="n">
-        <v>6428319</v>
+        <v>6428305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748878</v>
+        <v>122748802</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,35 +1797,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578923</v>
+        <v>578916</v>
       </c>
       <c r="R12" t="n">
-        <v>6428199</v>
+        <v>6428228</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1881,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748838</v>
+        <v>122748878</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,39 +1911,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578919</v>
+        <v>578923</v>
       </c>
       <c r="R13" t="n">
-        <v>6428218</v>
+        <v>6428199</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1991,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748778</v>
+        <v>122748608</v>
       </c>
       <c r="B14" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,29 +2022,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2057,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578907</v>
+        <v>578920</v>
       </c>
       <c r="R14" t="n">
-        <v>6428303</v>
+        <v>6428319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748625</v>
+        <v>122748824</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2168,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578926</v>
+        <v>578919</v>
       </c>
       <c r="R15" t="n">
-        <v>6428331</v>
+        <v>6428210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748513</v>
+        <v>122748491</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2279,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578874</v>
+        <v>578872</v>
       </c>
       <c r="R16" t="n">
-        <v>6428309</v>
+        <v>6428318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748865</v>
+        <v>122748700</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2390,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578923</v>
+        <v>578948</v>
       </c>
       <c r="R17" t="n">
-        <v>6428196</v>
+        <v>6428315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748650</v>
+        <v>122748625</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2501,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578934</v>
+        <v>578926</v>
       </c>
       <c r="R18" t="n">
-        <v>6428344</v>
+        <v>6428331</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748891</v>
+        <v>122748474</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2612,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578919</v>
+        <v>578871</v>
       </c>
       <c r="R19" t="n">
-        <v>6428209</v>
+        <v>6428320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748530</v>
+        <v>122748770</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2723,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578887</v>
+        <v>578907</v>
       </c>
       <c r="R20" t="n">
-        <v>6428305</v>
+        <v>6428303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748554</v>
+        <v>122748513</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2834,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578876</v>
+        <v>578874</v>
       </c>
       <c r="R21" t="n">
-        <v>6428319</v>
+        <v>6428309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748922</v>
+        <v>122748669</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>91362</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,46 +2910,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578971</v>
+        <v>578951</v>
       </c>
       <c r="R22" t="n">
-        <v>6428217</v>
+        <v>6428317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,7 +3012,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748450</v>
+        <v>122748637</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3059,7 +3063,7 @@
         <v>578855</v>
       </c>
       <c r="R23" t="n">
-        <v>6428306</v>
+        <v>6428305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,7 +3123,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748871</v>
+        <v>122748903</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3167,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578921</v>
+        <v>578994</v>
       </c>
       <c r="R24" t="n">
-        <v>6428203</v>
+        <v>6428205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748669</v>
+        <v>122748796</v>
       </c>
       <c r="B25" t="n">
-        <v>91362</v>
+        <v>57631</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,38 +3246,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3281,13 +3286,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578951</v>
+        <v>578916</v>
       </c>
       <c r="R25" t="n">
-        <v>6428317</v>
+        <v>6428228</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3325,7 +3330,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3455,10 +3459,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748817</v>
+        <v>122748852</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,35 +3471,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3503,13 +3507,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578912</v>
+        <v>578925</v>
       </c>
       <c r="R27" t="n">
-        <v>6428250</v>
+        <v>6428192</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3547,6 +3551,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748796</v>
+        <v>122748817</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,37 +3582,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3617,13 +3618,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578916</v>
+        <v>578912</v>
       </c>
       <c r="R28" t="n">
-        <v>6428228</v>
+        <v>6428250</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3679,10 +3680,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748974</v>
+        <v>122748778</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,33 +3692,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3727,10 +3724,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578879</v>
+        <v>578907</v>
       </c>
       <c r="R29" t="n">
-        <v>6428307</v>
+        <v>6428303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,7 +3787,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748474</v>
+        <v>122748749</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -3838,10 +3835,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578871</v>
+        <v>578854</v>
       </c>
       <c r="R30" t="n">
-        <v>6428320</v>
+        <v>6428300</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,7 +3898,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748749</v>
+        <v>122748974</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -3949,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578854</v>
+        <v>578879</v>
       </c>
       <c r="R31" t="n">
-        <v>6428300</v>
+        <v>6428307</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,10 +4009,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748824</v>
+        <v>122748838</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4024,35 +4021,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4063,10 +4064,10 @@
         <v>578919</v>
       </c>
       <c r="R32" t="n">
-        <v>6428210</v>
+        <v>6428218</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4104,7 +4105,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748491</v>
+        <v>122748650</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578872</v>
+        <v>578934</v>
       </c>
       <c r="R33" t="n">
-        <v>6428318</v>
+        <v>6428344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832101</v>
+        <v>122832817</v>
       </c>
       <c r="B34" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4246,29 +4246,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4278,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578875</v>
+        <v>578996</v>
       </c>
       <c r="R34" t="n">
-        <v>6428259</v>
+        <v>6428222</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4341,7 +4345,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832341</v>
+        <v>122832884</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4389,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578917</v>
+        <v>578944</v>
       </c>
       <c r="R35" t="n">
-        <v>6428212</v>
+        <v>6428183</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4452,7 +4456,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832295</v>
+        <v>122832530</v>
       </c>
       <c r="B36" t="n">
         <v>98365</v>
@@ -4500,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578916</v>
+        <v>578925</v>
       </c>
       <c r="R36" t="n">
-        <v>6428220</v>
+        <v>6428178</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4563,7 +4567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832254</v>
+        <v>122832730</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4611,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578889</v>
+        <v>578971</v>
       </c>
       <c r="R37" t="n">
-        <v>6428248</v>
+        <v>6428216</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4785,7 +4789,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832884</v>
+        <v>122832846</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4833,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578944</v>
+        <v>578992</v>
       </c>
       <c r="R39" t="n">
-        <v>6428183</v>
+        <v>6428165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,7 +4900,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832702</v>
+        <v>122832563</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4944,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578972</v>
+        <v>578948</v>
       </c>
       <c r="R40" t="n">
-        <v>6428239</v>
+        <v>6428141</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,7 +5011,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832846</v>
+        <v>122832784</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5055,10 +5059,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578992</v>
+        <v>578994</v>
       </c>
       <c r="R41" t="n">
-        <v>6428165</v>
+        <v>6428231</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,7 +5122,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832768</v>
+        <v>122832231</v>
       </c>
       <c r="B42" t="n">
         <v>98365</v>
@@ -5166,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578986</v>
+        <v>578889</v>
       </c>
       <c r="R42" t="n">
-        <v>6428221</v>
+        <v>6428243</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5229,7 +5233,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832231</v>
+        <v>122832750</v>
       </c>
       <c r="B43" t="n">
         <v>98365</v>
@@ -5277,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578889</v>
+        <v>578986</v>
       </c>
       <c r="R43" t="n">
-        <v>6428243</v>
+        <v>6428201</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5340,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832436</v>
+        <v>122832101</v>
       </c>
       <c r="B44" t="n">
-        <v>57631</v>
+        <v>95136</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5352,39 +5356,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5392,13 +5388,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578943</v>
+        <v>578875</v>
       </c>
       <c r="R44" t="n">
-        <v>6428212</v>
+        <v>6428259</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5436,6 +5432,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5454,7 +5451,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832662</v>
+        <v>122831927</v>
       </c>
       <c r="B45" t="n">
         <v>98365</v>
@@ -5502,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578900</v>
+        <v>578836</v>
       </c>
       <c r="R45" t="n">
-        <v>6428250</v>
+        <v>6428289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5565,7 +5562,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832400</v>
+        <v>122832134</v>
       </c>
       <c r="B46" t="n">
         <v>98365</v>
@@ -5613,10 +5610,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578935</v>
+        <v>578881</v>
       </c>
       <c r="R46" t="n">
-        <v>6428215</v>
+        <v>6428255</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5676,7 +5673,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832456</v>
+        <v>122832655</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -5724,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578914</v>
+        <v>578894</v>
       </c>
       <c r="R47" t="n">
-        <v>6428200</v>
+        <v>6428171</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5787,7 +5784,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832784</v>
+        <v>122832295</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -5835,10 +5832,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578994</v>
+        <v>578916</v>
       </c>
       <c r="R48" t="n">
-        <v>6428231</v>
+        <v>6428220</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5898,7 +5895,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832077</v>
+        <v>122832341</v>
       </c>
       <c r="B49" t="n">
         <v>98365</v>
@@ -5946,10 +5943,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578858</v>
+        <v>578917</v>
       </c>
       <c r="R49" t="n">
-        <v>6428260</v>
+        <v>6428212</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6006,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122831927</v>
+        <v>122832592</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6057,10 +6054,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578836</v>
+        <v>578925</v>
       </c>
       <c r="R50" t="n">
-        <v>6428289</v>
+        <v>6428157</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6120,7 +6117,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832134</v>
+        <v>122832077</v>
       </c>
       <c r="B51" t="n">
         <v>98365</v>
@@ -6168,10 +6165,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578881</v>
+        <v>578858</v>
       </c>
       <c r="R51" t="n">
-        <v>6428255</v>
+        <v>6428260</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6231,7 +6228,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832730</v>
+        <v>122832675</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6279,10 +6276,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578971</v>
+        <v>578924</v>
       </c>
       <c r="R52" t="n">
-        <v>6428216</v>
+        <v>6428234</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6342,10 +6339,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832655</v>
+        <v>122833108</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6354,35 +6351,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6390,13 +6391,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578894</v>
+        <v>578912</v>
       </c>
       <c r="R53" t="n">
-        <v>6428171</v>
+        <v>6428250</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6434,7 +6435,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122831868</v>
+        <v>122832254</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578848</v>
+        <v>578889</v>
       </c>
       <c r="R54" t="n">
-        <v>6428302</v>
+        <v>6428248</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832563</v>
+        <v>122831868</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578948</v>
+        <v>578848</v>
       </c>
       <c r="R55" t="n">
-        <v>6428141</v>
+        <v>6428302</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832383</v>
+        <v>122832208</v>
       </c>
       <c r="B56" t="n">
         <v>98365</v>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578929</v>
+        <v>578887</v>
       </c>
       <c r="R56" t="n">
-        <v>6428202</v>
+        <v>6428260</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832592</v>
+        <v>122832383</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578925</v>
+        <v>578929</v>
       </c>
       <c r="R57" t="n">
-        <v>6428157</v>
+        <v>6428202</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122833108</v>
+        <v>122832550</v>
       </c>
       <c r="B58" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6909,39 +6909,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6949,13 +6945,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578912</v>
+        <v>578934</v>
       </c>
       <c r="R58" t="n">
-        <v>6428250</v>
+        <v>6428155</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6993,6 +6989,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7122,7 +7119,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832817</v>
+        <v>122832768</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7170,10 +7167,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578996</v>
+        <v>578986</v>
       </c>
       <c r="R60" t="n">
-        <v>6428222</v>
+        <v>6428221</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7233,7 +7230,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832750</v>
+        <v>122832456</v>
       </c>
       <c r="B61" t="n">
         <v>98365</v>
@@ -7281,10 +7278,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578986</v>
+        <v>578914</v>
       </c>
       <c r="R61" t="n">
-        <v>6428201</v>
+        <v>6428200</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7344,7 +7341,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832530</v>
+        <v>122832400</v>
       </c>
       <c r="B62" t="n">
         <v>98365</v>
@@ -7392,10 +7389,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578925</v>
+        <v>578935</v>
       </c>
       <c r="R62" t="n">
-        <v>6428178</v>
+        <v>6428215</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7455,7 +7452,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832675</v>
+        <v>122832662</v>
       </c>
       <c r="B63" t="n">
         <v>98365</v>
@@ -7503,10 +7500,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578924</v>
+        <v>578900</v>
       </c>
       <c r="R63" t="n">
-        <v>6428234</v>
+        <v>6428250</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,7 +7563,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832208</v>
+        <v>122832702</v>
       </c>
       <c r="B64" t="n">
         <v>98365</v>
@@ -7614,10 +7611,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578887</v>
+        <v>578972</v>
       </c>
       <c r="R64" t="n">
-        <v>6428260</v>
+        <v>6428239</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7674,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832650</v>
+        <v>122832436</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7689,35 +7686,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7725,13 +7726,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578917</v>
+        <v>578943</v>
       </c>
       <c r="R65" t="n">
-        <v>6428142</v>
+        <v>6428212</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7769,7 +7770,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832550</v>
+        <v>122832650</v>
       </c>
       <c r="B66" t="n">
         <v>98365</v>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578934</v>
+        <v>578917</v>
       </c>
       <c r="R66" t="n">
-        <v>6428155</v>
+        <v>6428142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748491</v>
+        <v>122748700</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578872</v>
+        <v>578948</v>
       </c>
       <c r="R16" t="n">
-        <v>6428318</v>
+        <v>6428315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748700</v>
+        <v>122748491</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578948</v>
+        <v>578872</v>
       </c>
       <c r="R17" t="n">
-        <v>6428315</v>
+        <v>6428318</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748513</v>
+        <v>122748669</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>91362</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,35 +2799,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2835,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578874</v>
+        <v>578951</v>
       </c>
       <c r="R21" t="n">
-        <v>6428309</v>
+        <v>6428317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748669</v>
+        <v>122748513</v>
       </c>
       <c r="B22" t="n">
-        <v>91362</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,38 +2913,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578951</v>
+        <v>578874</v>
       </c>
       <c r="R22" t="n">
-        <v>6428317</v>
+        <v>6428309</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4456,7 +4456,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832530</v>
+        <v>122832730</v>
       </c>
       <c r="B36" t="n">
         <v>98365</v>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578925</v>
+        <v>578971</v>
       </c>
       <c r="R36" t="n">
-        <v>6428178</v>
+        <v>6428216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832730</v>
+        <v>122832530</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578971</v>
+        <v>578925</v>
       </c>
       <c r="R37" t="n">
-        <v>6428216</v>
+        <v>6428178</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6228,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832675</v>
+        <v>122833108</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6240,35 +6240,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6276,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578924</v>
+        <v>578912</v>
       </c>
       <c r="R52" t="n">
-        <v>6428234</v>
+        <v>6428250</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6320,7 +6324,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6339,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122833108</v>
+        <v>122832254</v>
       </c>
       <c r="B53" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6351,39 +6354,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6391,13 +6390,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578912</v>
+        <v>578889</v>
       </c>
       <c r="R53" t="n">
-        <v>6428250</v>
+        <v>6428248</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6435,6 +6434,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832254</v>
+        <v>122831868</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578889</v>
+        <v>578848</v>
       </c>
       <c r="R54" t="n">
-        <v>6428248</v>
+        <v>6428302</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122831868</v>
+        <v>122832208</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578848</v>
+        <v>578887</v>
       </c>
       <c r="R55" t="n">
-        <v>6428302</v>
+        <v>6428260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832208</v>
+        <v>122832675</v>
       </c>
       <c r="B56" t="n">
         <v>98365</v>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578887</v>
+        <v>578924</v>
       </c>
       <c r="R56" t="n">
-        <v>6428260</v>
+        <v>6428234</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7674,10 +7674,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832436</v>
+        <v>122832650</v>
       </c>
       <c r="B65" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7686,39 +7686,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7726,13 +7722,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578943</v>
+        <v>578917</v>
       </c>
       <c r="R65" t="n">
-        <v>6428212</v>
+        <v>6428142</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7770,6 +7766,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7788,10 +7785,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832650</v>
+        <v>122832436</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7800,35 +7797,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7836,13 +7837,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578917</v>
+        <v>578943</v>
       </c>
       <c r="R66" t="n">
-        <v>6428142</v>
+        <v>6428212</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7880,7 +7881,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748710</v>
+        <v>122748939</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578908</v>
+        <v>578966</v>
       </c>
       <c r="R2" t="n">
-        <v>6428300</v>
+        <v>6428216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748953</v>
+        <v>122748710</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578965</v>
+        <v>578908</v>
       </c>
       <c r="R3" t="n">
-        <v>6428213</v>
+        <v>6428300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748450</v>
+        <v>122748474</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578855</v>
+        <v>578871</v>
       </c>
       <c r="R4" t="n">
-        <v>6428306</v>
+        <v>6428320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748891</v>
+        <v>122748974</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578919</v>
+        <v>578879</v>
       </c>
       <c r="R5" t="n">
-        <v>6428209</v>
+        <v>6428307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748554</v>
+        <v>122748625</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578876</v>
+        <v>578926</v>
       </c>
       <c r="R6" t="n">
-        <v>6428319</v>
+        <v>6428331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748865</v>
+        <v>122748891</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578923</v>
+        <v>578919</v>
       </c>
       <c r="R7" t="n">
-        <v>6428196</v>
+        <v>6428209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748939</v>
+        <v>122748903</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578966</v>
+        <v>578994</v>
       </c>
       <c r="R8" t="n">
-        <v>6428216</v>
+        <v>6428205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748922</v>
+        <v>122748878</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1496,14 +1496,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578971</v>
+        <v>578923</v>
       </c>
       <c r="R9" t="n">
-        <v>6428217</v>
+        <v>6428199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748871</v>
+        <v>122748719</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578921</v>
+        <v>578907</v>
       </c>
       <c r="R10" t="n">
-        <v>6428203</v>
+        <v>6428320</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748530</v>
+        <v>122748770</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578887</v>
+        <v>578907</v>
       </c>
       <c r="R11" t="n">
-        <v>6428305</v>
+        <v>6428303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748802</v>
+        <v>122748796</v>
       </c>
       <c r="B12" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,37 +1797,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748878</v>
+        <v>122748838</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,35 +1911,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1947,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578923</v>
+        <v>578919</v>
       </c>
       <c r="R13" t="n">
-        <v>6428199</v>
+        <v>6428218</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748608</v>
+        <v>122748513</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2058,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578920</v>
+        <v>578874</v>
       </c>
       <c r="R14" t="n">
-        <v>6428319</v>
+        <v>6428309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748824</v>
+        <v>122748817</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,35 +2136,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,13 +2172,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578919</v>
+        <v>578912</v>
       </c>
       <c r="R15" t="n">
-        <v>6428210</v>
+        <v>6428250</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,7 +2216,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2232,7 +2234,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748700</v>
+        <v>122748637</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2280,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578948</v>
+        <v>578855</v>
       </c>
       <c r="R16" t="n">
-        <v>6428315</v>
+        <v>6428305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748491</v>
+        <v>122748778</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,33 +2357,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2391,10 +2389,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578872</v>
+        <v>578907</v>
       </c>
       <c r="R17" t="n">
-        <v>6428318</v>
+        <v>6428303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748625</v>
+        <v>122748824</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2502,10 +2500,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578926</v>
+        <v>578919</v>
       </c>
       <c r="R18" t="n">
-        <v>6428331</v>
+        <v>6428210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2563,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748474</v>
+        <v>122748450</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2613,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578871</v>
+        <v>578855</v>
       </c>
       <c r="R19" t="n">
-        <v>6428320</v>
+        <v>6428306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748770</v>
+        <v>122748554</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2724,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578907</v>
+        <v>578876</v>
       </c>
       <c r="R20" t="n">
-        <v>6428303</v>
+        <v>6428319</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748513</v>
+        <v>122748802</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,35 +2911,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2949,13 +2951,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578874</v>
+        <v>578916</v>
       </c>
       <c r="R22" t="n">
-        <v>6428309</v>
+        <v>6428228</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2993,7 +2995,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3012,7 +3013,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748637</v>
+        <v>122748922</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3056,14 +3057,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578855</v>
+        <v>578971</v>
       </c>
       <c r="R23" t="n">
-        <v>6428305</v>
+        <v>6428217</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,7 +3124,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748903</v>
+        <v>122748530</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3171,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578994</v>
+        <v>578887</v>
       </c>
       <c r="R24" t="n">
-        <v>6428205</v>
+        <v>6428305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748796</v>
+        <v>122748865</v>
       </c>
       <c r="B25" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,39 +3247,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3286,13 +3283,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578916</v>
+        <v>578923</v>
       </c>
       <c r="R25" t="n">
-        <v>6428228</v>
+        <v>6428196</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,6 +3327,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3348,7 +3346,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748719</v>
+        <v>122748871</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3396,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578907</v>
+        <v>578921</v>
       </c>
       <c r="R26" t="n">
-        <v>6428320</v>
+        <v>6428203</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3570,10 +3568,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748817</v>
+        <v>122748953</v>
       </c>
       <c r="B28" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3582,35 +3580,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3618,13 +3616,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578912</v>
+        <v>578965</v>
       </c>
       <c r="R28" t="n">
-        <v>6428250</v>
+        <v>6428213</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3662,6 +3660,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3680,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748778</v>
+        <v>122748608</v>
       </c>
       <c r="B29" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3692,29 +3691,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3724,10 +3727,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578907</v>
+        <v>578920</v>
       </c>
       <c r="R29" t="n">
-        <v>6428303</v>
+        <v>6428319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,7 +3790,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748749</v>
+        <v>122748700</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -3835,10 +3838,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578854</v>
+        <v>578948</v>
       </c>
       <c r="R30" t="n">
-        <v>6428300</v>
+        <v>6428315</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748974</v>
+        <v>122748749</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -3946,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578879</v>
+        <v>578854</v>
       </c>
       <c r="R31" t="n">
-        <v>6428307</v>
+        <v>6428300</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748838</v>
+        <v>122748491</v>
       </c>
       <c r="B32" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4021,39 +4024,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4061,13 +4060,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578919</v>
+        <v>578872</v>
       </c>
       <c r="R32" t="n">
-        <v>6428218</v>
+        <v>6428318</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4105,6 +4104,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832817</v>
+        <v>122832650</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578996</v>
+        <v>578917</v>
       </c>
       <c r="R34" t="n">
-        <v>6428222</v>
+        <v>6428142</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,7 +4345,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832884</v>
+        <v>122832750</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578944</v>
+        <v>578986</v>
       </c>
       <c r="R35" t="n">
-        <v>6428183</v>
+        <v>6428201</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,7 +4456,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832730</v>
+        <v>122832295</v>
       </c>
       <c r="B36" t="n">
         <v>98365</v>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578971</v>
+        <v>578916</v>
       </c>
       <c r="R36" t="n">
-        <v>6428216</v>
+        <v>6428220</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832530</v>
+        <v>122832592</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4618,7 +4618,7 @@
         <v>578925</v>
       </c>
       <c r="R37" t="n">
-        <v>6428178</v>
+        <v>6428157</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832157</v>
+        <v>122832986</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578886</v>
+        <v>578944</v>
       </c>
       <c r="R38" t="n">
-        <v>6428255</v>
+        <v>6428183</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832846</v>
+        <v>122832662</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578992</v>
+        <v>578900</v>
       </c>
       <c r="R39" t="n">
-        <v>6428165</v>
+        <v>6428250</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832563</v>
+        <v>122832134</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578948</v>
+        <v>578881</v>
       </c>
       <c r="R40" t="n">
-        <v>6428141</v>
+        <v>6428255</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832784</v>
+        <v>122832768</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578994</v>
+        <v>578986</v>
       </c>
       <c r="R41" t="n">
-        <v>6428231</v>
+        <v>6428221</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832231</v>
+        <v>122832702</v>
       </c>
       <c r="B42" t="n">
         <v>98365</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578889</v>
+        <v>578972</v>
       </c>
       <c r="R42" t="n">
-        <v>6428243</v>
+        <v>6428239</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832750</v>
+        <v>122832655</v>
       </c>
       <c r="B43" t="n">
         <v>98365</v>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578986</v>
+        <v>578894</v>
       </c>
       <c r="R43" t="n">
-        <v>6428201</v>
+        <v>6428171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832101</v>
+        <v>122832817</v>
       </c>
       <c r="B44" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5356,29 +5356,33 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5388,10 +5392,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578875</v>
+        <v>578996</v>
       </c>
       <c r="R44" t="n">
-        <v>6428259</v>
+        <v>6428222</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5451,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122831927</v>
+        <v>122832784</v>
       </c>
       <c r="B45" t="n">
         <v>98365</v>
@@ -5499,10 +5503,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578836</v>
+        <v>578994</v>
       </c>
       <c r="R45" t="n">
-        <v>6428289</v>
+        <v>6428231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5562,7 +5566,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832134</v>
+        <v>122832686</v>
       </c>
       <c r="B46" t="n">
         <v>98365</v>
@@ -5610,10 +5614,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578881</v>
+        <v>578971</v>
       </c>
       <c r="R46" t="n">
-        <v>6428255</v>
+        <v>6428232</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5673,7 +5677,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832655</v>
+        <v>122832550</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -5721,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578894</v>
+        <v>578934</v>
       </c>
       <c r="R47" t="n">
-        <v>6428171</v>
+        <v>6428155</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5784,7 +5788,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832295</v>
+        <v>122831927</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -5832,10 +5836,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578916</v>
+        <v>578836</v>
       </c>
       <c r="R48" t="n">
-        <v>6428220</v>
+        <v>6428289</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5895,7 +5899,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832341</v>
+        <v>122832208</v>
       </c>
       <c r="B49" t="n">
         <v>98365</v>
@@ -5943,10 +5947,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578917</v>
+        <v>578887</v>
       </c>
       <c r="R49" t="n">
-        <v>6428212</v>
+        <v>6428260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6006,7 +6010,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832592</v>
+        <v>122832675</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6054,10 +6058,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578925</v>
+        <v>578924</v>
       </c>
       <c r="R50" t="n">
-        <v>6428157</v>
+        <v>6428234</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6117,7 +6121,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832077</v>
+        <v>122832383</v>
       </c>
       <c r="B51" t="n">
         <v>98365</v>
@@ -6165,10 +6169,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578858</v>
+        <v>578929</v>
       </c>
       <c r="R51" t="n">
-        <v>6428260</v>
+        <v>6428202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,10 +6232,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122833108</v>
+        <v>122832436</v>
       </c>
       <c r="B52" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6240,37 +6244,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6280,13 +6284,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578912</v>
+        <v>578943</v>
       </c>
       <c r="R52" t="n">
-        <v>6428250</v>
+        <v>6428212</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6342,10 +6346,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832254</v>
+        <v>122833108</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6354,35 +6358,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6390,13 +6398,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578889</v>
+        <v>578912</v>
       </c>
       <c r="R53" t="n">
-        <v>6428248</v>
+        <v>6428250</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6434,7 +6442,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6453,7 +6460,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122831868</v>
+        <v>122832456</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6501,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578848</v>
+        <v>578914</v>
       </c>
       <c r="R54" t="n">
-        <v>6428302</v>
+        <v>6428200</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6571,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832208</v>
+        <v>122832945</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6612,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578887</v>
+        <v>578992</v>
       </c>
       <c r="R55" t="n">
-        <v>6428260</v>
+        <v>6428165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,7 +6682,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832675</v>
+        <v>122832231</v>
       </c>
       <c r="B56" t="n">
         <v>98365</v>
@@ -6723,10 +6730,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578924</v>
+        <v>578889</v>
       </c>
       <c r="R56" t="n">
-        <v>6428234</v>
+        <v>6428243</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6786,7 +6793,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832383</v>
+        <v>122832563</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -6834,10 +6841,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578929</v>
+        <v>578948</v>
       </c>
       <c r="R57" t="n">
-        <v>6428202</v>
+        <v>6428141</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6897,7 +6904,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832550</v>
+        <v>122831868</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -6945,10 +6952,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578934</v>
+        <v>578848</v>
       </c>
       <c r="R58" t="n">
-        <v>6428155</v>
+        <v>6428302</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7008,7 +7015,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832686</v>
+        <v>122832730</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7059,7 +7066,7 @@
         <v>578971</v>
       </c>
       <c r="R59" t="n">
-        <v>6428232</v>
+        <v>6428216</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7119,7 +7126,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832768</v>
+        <v>122832157</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7167,10 +7174,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578986</v>
+        <v>578886</v>
       </c>
       <c r="R60" t="n">
-        <v>6428221</v>
+        <v>6428255</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7230,7 +7237,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832456</v>
+        <v>122832530</v>
       </c>
       <c r="B61" t="n">
         <v>98365</v>
@@ -7278,10 +7285,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578914</v>
+        <v>578925</v>
       </c>
       <c r="R61" t="n">
-        <v>6428200</v>
+        <v>6428178</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7341,7 +7348,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832400</v>
+        <v>122832254</v>
       </c>
       <c r="B62" t="n">
         <v>98365</v>
@@ -7389,10 +7396,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578935</v>
+        <v>578889</v>
       </c>
       <c r="R62" t="n">
-        <v>6428215</v>
+        <v>6428248</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7452,10 +7459,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832662</v>
+        <v>122832101</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7464,33 +7471,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7500,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578900</v>
+        <v>578875</v>
       </c>
       <c r="R63" t="n">
-        <v>6428250</v>
+        <v>6428259</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7563,7 +7566,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832702</v>
+        <v>122832341</v>
       </c>
       <c r="B64" t="n">
         <v>98365</v>
@@ -7611,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578972</v>
+        <v>578917</v>
       </c>
       <c r="R64" t="n">
-        <v>6428239</v>
+        <v>6428212</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7674,7 +7677,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832650</v>
+        <v>122832400</v>
       </c>
       <c r="B65" t="n">
         <v>98365</v>
@@ -7722,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578917</v>
+        <v>578935</v>
       </c>
       <c r="R65" t="n">
-        <v>6428142</v>
+        <v>6428215</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7785,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832436</v>
+        <v>122832077</v>
       </c>
       <c r="B66" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7797,39 +7800,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7837,13 +7836,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578943</v>
+        <v>578858</v>
       </c>
       <c r="R66" t="n">
-        <v>6428212</v>
+        <v>6428260</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7881,6 +7880,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748939</v>
+        <v>122748749</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578966</v>
+        <v>578854</v>
       </c>
       <c r="R2" t="n">
-        <v>6428216</v>
+        <v>6428300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748710</v>
+        <v>122748974</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578908</v>
+        <v>578879</v>
       </c>
       <c r="R3" t="n">
-        <v>6428300</v>
+        <v>6428307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748474</v>
+        <v>122748871</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578871</v>
+        <v>578921</v>
       </c>
       <c r="R4" t="n">
-        <v>6428320</v>
+        <v>6428203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748974</v>
+        <v>122748700</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578879</v>
+        <v>578948</v>
       </c>
       <c r="R5" t="n">
-        <v>6428307</v>
+        <v>6428315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748625</v>
+        <v>122748554</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578926</v>
+        <v>578876</v>
       </c>
       <c r="R6" t="n">
-        <v>6428331</v>
+        <v>6428319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748891</v>
+        <v>122748824</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1281,7 +1281,7 @@
         <v>578919</v>
       </c>
       <c r="R7" t="n">
-        <v>6428209</v>
+        <v>6428210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748903</v>
+        <v>122748838</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,35 +1353,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578994</v>
+        <v>578919</v>
       </c>
       <c r="R8" t="n">
-        <v>6428205</v>
+        <v>6428218</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,7 +1437,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748878</v>
+        <v>122748778</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,33 +1467,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1500,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578923</v>
+        <v>578907</v>
       </c>
       <c r="R9" t="n">
-        <v>6428199</v>
+        <v>6428303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748719</v>
+        <v>122748491</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1611,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578907</v>
+        <v>578872</v>
       </c>
       <c r="R10" t="n">
-        <v>6428320</v>
+        <v>6428318</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748770</v>
+        <v>122748625</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1722,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578907</v>
+        <v>578926</v>
       </c>
       <c r="R11" t="n">
-        <v>6428303</v>
+        <v>6428331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748796</v>
+        <v>122748530</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,39 +1796,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1837,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578916</v>
+        <v>578887</v>
       </c>
       <c r="R12" t="n">
-        <v>6428228</v>
+        <v>6428305</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,6 +1876,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1899,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748838</v>
+        <v>122748878</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,39 +1907,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,13 +1943,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578919</v>
+        <v>578923</v>
       </c>
       <c r="R13" t="n">
-        <v>6428218</v>
+        <v>6428199</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1987,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,7 +2006,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748513</v>
+        <v>122748891</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2061,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578874</v>
+        <v>578919</v>
       </c>
       <c r="R14" t="n">
-        <v>6428309</v>
+        <v>6428209</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748817</v>
+        <v>122748710</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,35 +2129,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2172,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578912</v>
+        <v>578908</v>
       </c>
       <c r="R15" t="n">
-        <v>6428250</v>
+        <v>6428300</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,6 +2209,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2234,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748637</v>
+        <v>122748817</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>56688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,35 +2240,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2282,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578855</v>
+        <v>578912</v>
       </c>
       <c r="R16" t="n">
-        <v>6428305</v>
+        <v>6428250</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2320,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2345,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748778</v>
+        <v>122748796</v>
       </c>
       <c r="B17" t="n">
-        <v>95136</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,31 +2350,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2389,13 +2390,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578907</v>
+        <v>578916</v>
       </c>
       <c r="R17" t="n">
-        <v>6428303</v>
+        <v>6428228</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2434,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748824</v>
+        <v>122748770</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578919</v>
+        <v>578907</v>
       </c>
       <c r="R18" t="n">
-        <v>6428210</v>
+        <v>6428303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748450</v>
+        <v>122748637</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2614,7 +2614,7 @@
         <v>578855</v>
       </c>
       <c r="R19" t="n">
-        <v>6428306</v>
+        <v>6428305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748554</v>
+        <v>122748865</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578876</v>
+        <v>578923</v>
       </c>
       <c r="R20" t="n">
-        <v>6428319</v>
+        <v>6428196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748802</v>
+        <v>122748922</v>
       </c>
       <c r="B22" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,53 +2911,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578916</v>
+        <v>578971</v>
       </c>
       <c r="R22" t="n">
-        <v>6428228</v>
+        <v>6428217</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2995,6 +2991,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3013,7 +3010,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748922</v>
+        <v>122748903</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3057,14 +3054,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578971</v>
+        <v>578994</v>
       </c>
       <c r="R23" t="n">
-        <v>6428217</v>
+        <v>6428205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3124,7 +3121,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748530</v>
+        <v>122748650</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3172,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578887</v>
+        <v>578934</v>
       </c>
       <c r="R24" t="n">
-        <v>6428305</v>
+        <v>6428344</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,7 +3232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748865</v>
+        <v>122748719</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3283,10 +3280,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578923</v>
+        <v>578907</v>
       </c>
       <c r="R25" t="n">
-        <v>6428196</v>
+        <v>6428320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748871</v>
+        <v>122748802</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3358,35 +3355,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3394,13 +3395,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578921</v>
+        <v>578916</v>
       </c>
       <c r="R26" t="n">
-        <v>6428203</v>
+        <v>6428228</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3439,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748852</v>
+        <v>122748939</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578925</v>
+        <v>578966</v>
       </c>
       <c r="R27" t="n">
-        <v>6428192</v>
+        <v>6428216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748953</v>
+        <v>122748450</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578965</v>
+        <v>578855</v>
       </c>
       <c r="R28" t="n">
-        <v>6428213</v>
+        <v>6428306</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748608</v>
+        <v>122748953</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578920</v>
+        <v>578965</v>
       </c>
       <c r="R29" t="n">
-        <v>6428319</v>
+        <v>6428213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748700</v>
+        <v>122748608</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578948</v>
+        <v>578920</v>
       </c>
       <c r="R30" t="n">
-        <v>6428315</v>
+        <v>6428319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748749</v>
+        <v>122748474</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578854</v>
+        <v>578871</v>
       </c>
       <c r="R31" t="n">
-        <v>6428300</v>
+        <v>6428320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748491</v>
+        <v>122748513</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578872</v>
+        <v>578874</v>
       </c>
       <c r="R32" t="n">
-        <v>6428318</v>
+        <v>6428309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748650</v>
+        <v>122748852</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578934</v>
+        <v>578925</v>
       </c>
       <c r="R33" t="n">
-        <v>6428344</v>
+        <v>6428192</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832650</v>
+        <v>122832768</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578917</v>
+        <v>578986</v>
       </c>
       <c r="R34" t="n">
-        <v>6428142</v>
+        <v>6428221</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,7 +4345,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832750</v>
+        <v>122832077</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578986</v>
+        <v>578858</v>
       </c>
       <c r="R35" t="n">
-        <v>6428201</v>
+        <v>6428260</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832295</v>
+        <v>122832101</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4468,33 +4468,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4504,10 +4500,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578916</v>
+        <v>578875</v>
       </c>
       <c r="R36" t="n">
-        <v>6428220</v>
+        <v>6428259</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,7 +4563,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832592</v>
+        <v>122832550</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4615,10 +4611,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578925</v>
+        <v>578934</v>
       </c>
       <c r="R37" t="n">
-        <v>6428157</v>
+        <v>6428155</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,7 +4674,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832986</v>
+        <v>122832295</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4726,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578944</v>
+        <v>578916</v>
       </c>
       <c r="R38" t="n">
-        <v>6428183</v>
+        <v>6428220</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,7 +4785,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832662</v>
+        <v>122832986</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4837,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578900</v>
+        <v>578944</v>
       </c>
       <c r="R39" t="n">
-        <v>6428250</v>
+        <v>6428183</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4900,7 +4896,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832134</v>
+        <v>122832208</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4948,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578881</v>
+        <v>578887</v>
       </c>
       <c r="R40" t="n">
-        <v>6428255</v>
+        <v>6428260</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5011,7 +5007,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832768</v>
+        <v>122832530</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5059,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578986</v>
+        <v>578925</v>
       </c>
       <c r="R41" t="n">
-        <v>6428221</v>
+        <v>6428178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5122,7 +5118,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832702</v>
+        <v>122831868</v>
       </c>
       <c r="B42" t="n">
         <v>98365</v>
@@ -5170,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578972</v>
+        <v>578848</v>
       </c>
       <c r="R42" t="n">
-        <v>6428239</v>
+        <v>6428302</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,10 +5229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832655</v>
+        <v>122832436</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5245,35 +5241,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578894</v>
+        <v>578943</v>
       </c>
       <c r="R43" t="n">
-        <v>6428171</v>
+        <v>6428212</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5325,7 +5325,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5344,7 +5343,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832817</v>
+        <v>122832846</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5392,10 +5391,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578996</v>
+        <v>578992</v>
       </c>
       <c r="R44" t="n">
-        <v>6428222</v>
+        <v>6428165</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,7 +5454,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832784</v>
+        <v>122832134</v>
       </c>
       <c r="B45" t="n">
         <v>98365</v>
@@ -5503,10 +5502,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578994</v>
+        <v>578881</v>
       </c>
       <c r="R45" t="n">
-        <v>6428231</v>
+        <v>6428255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,7 +5565,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832686</v>
+        <v>122832655</v>
       </c>
       <c r="B46" t="n">
         <v>98365</v>
@@ -5614,10 +5613,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578971</v>
+        <v>578894</v>
       </c>
       <c r="R46" t="n">
-        <v>6428232</v>
+        <v>6428171</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,7 +5676,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832550</v>
+        <v>122832592</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -5725,10 +5724,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578934</v>
+        <v>578925</v>
       </c>
       <c r="R47" t="n">
-        <v>6428155</v>
+        <v>6428157</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,7 +5787,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122831927</v>
+        <v>122832784</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -5836,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578836</v>
+        <v>578994</v>
       </c>
       <c r="R48" t="n">
-        <v>6428289</v>
+        <v>6428231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5899,7 +5898,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832208</v>
+        <v>122832817</v>
       </c>
       <c r="B49" t="n">
         <v>98365</v>
@@ -5947,10 +5946,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578887</v>
+        <v>578996</v>
       </c>
       <c r="R49" t="n">
-        <v>6428260</v>
+        <v>6428222</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6010,7 +6009,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832675</v>
+        <v>122832563</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6058,10 +6057,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578924</v>
+        <v>578948</v>
       </c>
       <c r="R50" t="n">
-        <v>6428234</v>
+        <v>6428141</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6120,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832383</v>
+        <v>122832662</v>
       </c>
       <c r="B51" t="n">
         <v>98365</v>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578929</v>
+        <v>578900</v>
       </c>
       <c r="R51" t="n">
-        <v>6428202</v>
+        <v>6428250</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6232,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832436</v>
+        <v>122832231</v>
       </c>
       <c r="B52" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6244,39 +6243,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6284,13 +6279,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578943</v>
+        <v>578889</v>
       </c>
       <c r="R52" t="n">
-        <v>6428212</v>
+        <v>6428243</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6328,6 +6323,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6346,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122833108</v>
+        <v>122832254</v>
       </c>
       <c r="B53" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6358,39 +6354,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6398,13 +6390,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578912</v>
+        <v>578889</v>
       </c>
       <c r="R53" t="n">
-        <v>6428250</v>
+        <v>6428248</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6442,6 +6434,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6571,7 +6564,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832945</v>
+        <v>122832341</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6619,10 +6612,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578992</v>
+        <v>578917</v>
       </c>
       <c r="R55" t="n">
-        <v>6428165</v>
+        <v>6428212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6682,7 +6675,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832231</v>
+        <v>122832675</v>
       </c>
       <c r="B56" t="n">
         <v>98365</v>
@@ -6730,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578889</v>
+        <v>578924</v>
       </c>
       <c r="R56" t="n">
-        <v>6428243</v>
+        <v>6428234</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6793,7 +6786,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832563</v>
+        <v>122832750</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -6841,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578948</v>
+        <v>578986</v>
       </c>
       <c r="R57" t="n">
-        <v>6428141</v>
+        <v>6428201</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,7 +6897,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122831868</v>
+        <v>122832702</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -6952,10 +6945,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578848</v>
+        <v>578972</v>
       </c>
       <c r="R58" t="n">
-        <v>6428302</v>
+        <v>6428239</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7015,7 +7008,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832730</v>
+        <v>122832383</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7063,10 +7056,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578971</v>
+        <v>578929</v>
       </c>
       <c r="R59" t="n">
-        <v>6428216</v>
+        <v>6428202</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7126,7 +7119,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832157</v>
+        <v>122832650</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7174,10 +7167,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578886</v>
+        <v>578917</v>
       </c>
       <c r="R60" t="n">
-        <v>6428255</v>
+        <v>6428142</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7237,7 +7230,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832530</v>
+        <v>122832730</v>
       </c>
       <c r="B61" t="n">
         <v>98365</v>
@@ -7285,10 +7278,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578925</v>
+        <v>578971</v>
       </c>
       <c r="R61" t="n">
-        <v>6428178</v>
+        <v>6428216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7348,10 +7341,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832254</v>
+        <v>122833108</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7360,35 +7353,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7396,13 +7393,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578889</v>
+        <v>578912</v>
       </c>
       <c r="R62" t="n">
-        <v>6428248</v>
+        <v>6428250</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7440,7 +7437,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7459,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832101</v>
+        <v>122832686</v>
       </c>
       <c r="B63" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7471,29 +7467,33 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578875</v>
+        <v>578971</v>
       </c>
       <c r="R63" t="n">
-        <v>6428259</v>
+        <v>6428232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,7 +7566,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832341</v>
+        <v>122832400</v>
       </c>
       <c r="B64" t="n">
         <v>98365</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578917</v>
+        <v>578935</v>
       </c>
       <c r="R64" t="n">
-        <v>6428212</v>
+        <v>6428215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832400</v>
+        <v>122831927</v>
       </c>
       <c r="B65" t="n">
         <v>98365</v>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578935</v>
+        <v>578836</v>
       </c>
       <c r="R65" t="n">
-        <v>6428215</v>
+        <v>6428289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832077</v>
+        <v>122832157</v>
       </c>
       <c r="B66" t="n">
         <v>98365</v>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578858</v>
+        <v>578886</v>
       </c>
       <c r="R66" t="n">
-        <v>6428260</v>
+        <v>6428255</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -2006,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748891</v>
+        <v>122748817</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,35 +2018,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578919</v>
+        <v>578912</v>
       </c>
       <c r="R14" t="n">
-        <v>6428209</v>
+        <v>6428250</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748710</v>
+        <v>122748796</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,35 +2128,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2165,13 +2168,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578908</v>
+        <v>578916</v>
       </c>
       <c r="R15" t="n">
-        <v>6428300</v>
+        <v>6428228</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2212,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748817</v>
+        <v>122748891</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,35 +2242,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2276,13 +2278,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578912</v>
+        <v>578919</v>
       </c>
       <c r="R16" t="n">
-        <v>6428250</v>
+        <v>6428209</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,6 +2322,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2338,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748796</v>
+        <v>122748710</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2350,39 +2353,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2390,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578916</v>
+        <v>578908</v>
       </c>
       <c r="R17" t="n">
-        <v>6428228</v>
+        <v>6428300</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,6 +2433,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832986</v>
+        <v>122832208</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578944</v>
+        <v>578887</v>
       </c>
       <c r="R39" t="n">
-        <v>6428183</v>
+        <v>6428260</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832208</v>
+        <v>122832530</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578887</v>
+        <v>578925</v>
       </c>
       <c r="R40" t="n">
-        <v>6428260</v>
+        <v>6428178</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832530</v>
+        <v>122832986</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578925</v>
+        <v>578944</v>
       </c>
       <c r="R41" t="n">
-        <v>6428178</v>
+        <v>6428183</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122833108</v>
+        <v>122832686</v>
       </c>
       <c r="B62" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7353,39 +7353,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7393,13 +7389,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578912</v>
+        <v>578971</v>
       </c>
       <c r="R62" t="n">
-        <v>6428250</v>
+        <v>6428232</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7437,6 +7433,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7455,10 +7452,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832686</v>
+        <v>122833108</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7467,35 +7464,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7503,13 +7504,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578971</v>
+        <v>578912</v>
       </c>
       <c r="R63" t="n">
-        <v>6428232</v>
+        <v>6428250</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7547,7 +7548,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -4785,7 +4785,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832208</v>
+        <v>122832986</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578887</v>
+        <v>578944</v>
       </c>
       <c r="R39" t="n">
-        <v>6428260</v>
+        <v>6428183</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832530</v>
+        <v>122832208</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578925</v>
+        <v>578887</v>
       </c>
       <c r="R40" t="n">
-        <v>6428178</v>
+        <v>6428260</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832986</v>
+        <v>122832530</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578944</v>
+        <v>578925</v>
       </c>
       <c r="R41" t="n">
-        <v>6428183</v>
+        <v>6428178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748749</v>
+        <v>122748871</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578854</v>
+        <v>578921</v>
       </c>
       <c r="R2" t="n">
-        <v>6428300</v>
+        <v>6428203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748974</v>
+        <v>122748719</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578879</v>
+        <v>578907</v>
       </c>
       <c r="R3" t="n">
-        <v>6428307</v>
+        <v>6428320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748871</v>
+        <v>122748491</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578921</v>
+        <v>578872</v>
       </c>
       <c r="R4" t="n">
-        <v>6428203</v>
+        <v>6428318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748700</v>
+        <v>122748802</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1020,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578948</v>
+        <v>578916</v>
       </c>
       <c r="R5" t="n">
-        <v>6428315</v>
+        <v>6428228</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748554</v>
+        <v>122748700</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578876</v>
+        <v>578948</v>
       </c>
       <c r="R6" t="n">
-        <v>6428319</v>
+        <v>6428315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748824</v>
+        <v>122748852</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578919</v>
+        <v>578925</v>
       </c>
       <c r="R7" t="n">
-        <v>6428210</v>
+        <v>6428192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748838</v>
+        <v>122748953</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578919</v>
+        <v>578965</v>
       </c>
       <c r="R8" t="n">
-        <v>6428218</v>
+        <v>6428213</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,6 +1436,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748778</v>
+        <v>122748824</v>
       </c>
       <c r="B9" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,29 +1467,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1499,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578907</v>
+        <v>578919</v>
       </c>
       <c r="R9" t="n">
-        <v>6428303</v>
+        <v>6428210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748491</v>
+        <v>122748796</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,35 +1578,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578872</v>
+        <v>578916</v>
       </c>
       <c r="R10" t="n">
-        <v>6428318</v>
+        <v>6428228</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1662,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1673,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748625</v>
+        <v>122748637</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578926</v>
+        <v>578855</v>
       </c>
       <c r="R11" t="n">
-        <v>6428331</v>
+        <v>6428305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748530</v>
+        <v>122748513</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578887</v>
+        <v>578874</v>
       </c>
       <c r="R12" t="n">
-        <v>6428305</v>
+        <v>6428309</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748878</v>
+        <v>122748770</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578923</v>
+        <v>578907</v>
       </c>
       <c r="R13" t="n">
-        <v>6428199</v>
+        <v>6428303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748817</v>
+        <v>122748939</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,35 +2025,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2054,13 +2061,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578912</v>
+        <v>578966</v>
       </c>
       <c r="R14" t="n">
-        <v>6428250</v>
+        <v>6428216</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,6 +2105,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2116,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748796</v>
+        <v>122748903</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,39 +2136,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2168,13 +2172,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578916</v>
+        <v>578994</v>
       </c>
       <c r="R15" t="n">
-        <v>6428228</v>
+        <v>6428205</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,6 +2216,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2230,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748891</v>
+        <v>122748838</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,35 +2247,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2281,10 +2290,10 @@
         <v>578919</v>
       </c>
       <c r="R16" t="n">
-        <v>6428209</v>
+        <v>6428218</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2322,7 +2331,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2341,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748710</v>
+        <v>122748891</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578908</v>
+        <v>578919</v>
       </c>
       <c r="R17" t="n">
-        <v>6428300</v>
+        <v>6428209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748770</v>
+        <v>122748625</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578907</v>
+        <v>578926</v>
       </c>
       <c r="R18" t="n">
-        <v>6428303</v>
+        <v>6428331</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748637</v>
+        <v>122748450</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2614,7 +2622,7 @@
         <v>578855</v>
       </c>
       <c r="R19" t="n">
-        <v>6428305</v>
+        <v>6428306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748865</v>
+        <v>122748878</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2725,7 +2733,7 @@
         <v>578923</v>
       </c>
       <c r="R20" t="n">
-        <v>6428196</v>
+        <v>6428199</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748669</v>
+        <v>122748865</v>
       </c>
       <c r="B21" t="n">
-        <v>91362</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,38 +2805,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578951</v>
+        <v>578923</v>
       </c>
       <c r="R21" t="n">
-        <v>6428317</v>
+        <v>6428196</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,10 +2904,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748922</v>
+        <v>122748554</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,14 +2948,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578971</v>
+        <v>578876</v>
       </c>
       <c r="R22" t="n">
-        <v>6428217</v>
+        <v>6428319</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122748903</v>
+        <v>122748974</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578994</v>
+        <v>578879</v>
       </c>
       <c r="R23" t="n">
-        <v>6428205</v>
+        <v>6428307</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748650</v>
+        <v>122748530</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578934</v>
+        <v>578887</v>
       </c>
       <c r="R24" t="n">
-        <v>6428344</v>
+        <v>6428305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3232,10 +3237,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748719</v>
+        <v>122748922</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,14 +3281,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578907</v>
+        <v>578971</v>
       </c>
       <c r="R25" t="n">
-        <v>6428320</v>
+        <v>6428217</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3343,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748802</v>
+        <v>122748710</v>
       </c>
       <c r="B26" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3355,39 +3360,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3395,13 +3396,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578916</v>
+        <v>578908</v>
       </c>
       <c r="R26" t="n">
-        <v>6428228</v>
+        <v>6428300</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3439,6 +3440,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3457,10 +3459,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748939</v>
+        <v>122748778</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3469,33 +3471,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3505,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578966</v>
+        <v>578907</v>
       </c>
       <c r="R27" t="n">
-        <v>6428216</v>
+        <v>6428303</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748450</v>
+        <v>122748474</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578855</v>
+        <v>578871</v>
       </c>
       <c r="R28" t="n">
-        <v>6428306</v>
+        <v>6428320</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748953</v>
+        <v>122748650</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3727,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578965</v>
+        <v>578934</v>
       </c>
       <c r="R29" t="n">
-        <v>6428213</v>
+        <v>6428344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748608</v>
+        <v>122748817</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>56691</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3802,35 +3800,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3838,13 +3836,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578920</v>
+        <v>578912</v>
       </c>
       <c r="R30" t="n">
-        <v>6428319</v>
+        <v>6428250</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3882,7 +3880,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3901,10 +3898,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748474</v>
+        <v>122748669</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>91365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3913,35 +3910,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578871</v>
+        <v>578951</v>
       </c>
       <c r="R31" t="n">
-        <v>6428320</v>
+        <v>6428317</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748513</v>
+        <v>122748749</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578874</v>
+        <v>578854</v>
       </c>
       <c r="R32" t="n">
-        <v>6428309</v>
+        <v>6428300</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748852</v>
+        <v>122748608</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578925</v>
+        <v>578920</v>
       </c>
       <c r="R33" t="n">
-        <v>6428192</v>
+        <v>6428319</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832768</v>
+        <v>122832655</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578986</v>
+        <v>578894</v>
       </c>
       <c r="R34" t="n">
-        <v>6428221</v>
+        <v>6428171</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832077</v>
+        <v>122832750</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578858</v>
+        <v>578986</v>
       </c>
       <c r="R35" t="n">
-        <v>6428260</v>
+        <v>6428201</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832101</v>
+        <v>122832231</v>
       </c>
       <c r="B36" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4468,29 +4468,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4500,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578875</v>
+        <v>578889</v>
       </c>
       <c r="R36" t="n">
-        <v>6428259</v>
+        <v>6428243</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4563,10 +4567,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832550</v>
+        <v>122832341</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4611,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578934</v>
+        <v>578917</v>
       </c>
       <c r="R37" t="n">
-        <v>6428155</v>
+        <v>6428212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4674,10 +4678,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832295</v>
+        <v>122832134</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578916</v>
+        <v>578881</v>
       </c>
       <c r="R38" t="n">
-        <v>6428220</v>
+        <v>6428255</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4785,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832986</v>
+        <v>122832456</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4833,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578944</v>
+        <v>578914</v>
       </c>
       <c r="R39" t="n">
-        <v>6428183</v>
+        <v>6428200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832208</v>
+        <v>122832675</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4944,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578887</v>
+        <v>578924</v>
       </c>
       <c r="R40" t="n">
-        <v>6428260</v>
+        <v>6428234</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,10 +5011,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832530</v>
+        <v>122832563</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5055,10 +5059,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578925</v>
+        <v>578948</v>
       </c>
       <c r="R41" t="n">
-        <v>6428178</v>
+        <v>6428141</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122831868</v>
+        <v>122832702</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5166,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578848</v>
+        <v>578972</v>
       </c>
       <c r="R42" t="n">
-        <v>6428302</v>
+        <v>6428239</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5229,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832436</v>
+        <v>122832254</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>98368</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5241,39 +5245,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578943</v>
+        <v>578889</v>
       </c>
       <c r="R43" t="n">
-        <v>6428212</v>
+        <v>6428248</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5325,6 +5325,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5343,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832846</v>
+        <v>122831927</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5391,10 +5392,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578992</v>
+        <v>578836</v>
       </c>
       <c r="R44" t="n">
-        <v>6428165</v>
+        <v>6428289</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832134</v>
+        <v>122832157</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5502,7 +5503,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578881</v>
+        <v>578886</v>
       </c>
       <c r="R45" t="n">
         <v>6428255</v>
@@ -5565,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832655</v>
+        <v>122832383</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5613,10 +5614,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578894</v>
+        <v>578929</v>
       </c>
       <c r="R46" t="n">
-        <v>6428171</v>
+        <v>6428202</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5676,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832592</v>
+        <v>122832530</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5727,7 +5728,7 @@
         <v>578925</v>
       </c>
       <c r="R47" t="n">
-        <v>6428157</v>
+        <v>6428178</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5787,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832784</v>
+        <v>122832436</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>57634</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,35 +5800,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5835,13 +5840,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578994</v>
+        <v>578943</v>
       </c>
       <c r="R48" t="n">
-        <v>6428231</v>
+        <v>6428212</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5879,7 +5884,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5898,10 +5902,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832817</v>
+        <v>122832730</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5946,10 +5950,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578996</v>
+        <v>578971</v>
       </c>
       <c r="R49" t="n">
-        <v>6428222</v>
+        <v>6428216</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,10 +6013,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832563</v>
+        <v>122832662</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6057,10 +6061,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578948</v>
+        <v>578900</v>
       </c>
       <c r="R50" t="n">
-        <v>6428141</v>
+        <v>6428250</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6120,10 +6124,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832662</v>
+        <v>122832817</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,10 +6172,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578900</v>
+        <v>578996</v>
       </c>
       <c r="R51" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6231,10 +6235,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832231</v>
+        <v>122832077</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6279,10 +6283,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578889</v>
+        <v>578858</v>
       </c>
       <c r="R52" t="n">
-        <v>6428243</v>
+        <v>6428260</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6342,10 +6346,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832254</v>
+        <v>122833108</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6354,35 +6358,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6390,13 +6398,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578889</v>
+        <v>578912</v>
       </c>
       <c r="R53" t="n">
-        <v>6428248</v>
+        <v>6428250</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6434,7 +6442,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6453,10 +6460,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832456</v>
+        <v>122832550</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6501,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578914</v>
+        <v>578934</v>
       </c>
       <c r="R54" t="n">
-        <v>6428200</v>
+        <v>6428155</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,10 +6571,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832341</v>
+        <v>122832784</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6612,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578917</v>
+        <v>578994</v>
       </c>
       <c r="R55" t="n">
-        <v>6428212</v>
+        <v>6428231</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,10 +6682,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832675</v>
+        <v>122832986</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6723,10 +6730,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578924</v>
+        <v>578944</v>
       </c>
       <c r="R56" t="n">
-        <v>6428234</v>
+        <v>6428183</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6786,10 +6793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832750</v>
+        <v>122832846</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6834,10 +6841,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578986</v>
+        <v>578992</v>
       </c>
       <c r="R57" t="n">
-        <v>6428201</v>
+        <v>6428165</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6897,10 +6904,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832702</v>
+        <v>122831868</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6945,10 +6952,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578972</v>
+        <v>578848</v>
       </c>
       <c r="R58" t="n">
-        <v>6428239</v>
+        <v>6428302</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7008,10 +7015,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832383</v>
+        <v>122832592</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7056,10 +7063,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578929</v>
+        <v>578925</v>
       </c>
       <c r="R59" t="n">
-        <v>6428202</v>
+        <v>6428157</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7119,10 +7126,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832650</v>
+        <v>122832686</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7167,10 +7174,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578917</v>
+        <v>578971</v>
       </c>
       <c r="R60" t="n">
-        <v>6428142</v>
+        <v>6428232</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7230,10 +7237,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832730</v>
+        <v>122832101</v>
       </c>
       <c r="B61" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7242,33 +7249,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7278,10 +7281,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578971</v>
+        <v>578875</v>
       </c>
       <c r="R61" t="n">
-        <v>6428216</v>
+        <v>6428259</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7341,10 +7344,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832686</v>
+        <v>122832400</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7389,10 +7392,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578971</v>
+        <v>578935</v>
       </c>
       <c r="R62" t="n">
-        <v>6428232</v>
+        <v>6428215</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7452,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122833108</v>
+        <v>122832768</v>
       </c>
       <c r="B63" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7464,39 +7467,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7504,13 +7503,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578912</v>
+        <v>578986</v>
       </c>
       <c r="R63" t="n">
-        <v>6428250</v>
+        <v>6428221</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7548,6 +7547,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832400</v>
+        <v>122832650</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578935</v>
+        <v>578917</v>
       </c>
       <c r="R64" t="n">
-        <v>6428215</v>
+        <v>6428142</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122831927</v>
+        <v>122832208</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578836</v>
+        <v>578887</v>
       </c>
       <c r="R65" t="n">
-        <v>6428289</v>
+        <v>6428260</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832157</v>
+        <v>122832295</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578886</v>
+        <v>578916</v>
       </c>
       <c r="R66" t="n">
-        <v>6428255</v>
+        <v>6428220</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748871</v>
+        <v>122748719</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578921</v>
+        <v>578907</v>
       </c>
       <c r="R2" t="n">
-        <v>6428203</v>
+        <v>6428320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748719</v>
+        <v>122748692</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578907</v>
+        <v>578948</v>
       </c>
       <c r="R3" t="n">
-        <v>6428320</v>
+        <v>6428315</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748491</v>
+        <v>122748637</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578872</v>
+        <v>578855</v>
       </c>
       <c r="R4" t="n">
-        <v>6428318</v>
+        <v>6428305</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748802</v>
+        <v>122748491</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,39 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578916</v>
+        <v>578872</v>
       </c>
       <c r="R5" t="n">
-        <v>6428228</v>
+        <v>6428318</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,6 +1100,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748700</v>
+        <v>122748939</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578948</v>
+        <v>578966</v>
       </c>
       <c r="R6" t="n">
-        <v>6428315</v>
+        <v>6428216</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748852</v>
+        <v>122748824</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578925</v>
+        <v>578919</v>
       </c>
       <c r="R7" t="n">
-        <v>6428192</v>
+        <v>6428210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748953</v>
+        <v>122748625</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578965</v>
+        <v>578926</v>
       </c>
       <c r="R8" t="n">
-        <v>6428213</v>
+        <v>6428331</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748824</v>
+        <v>122748903</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578919</v>
+        <v>578994</v>
       </c>
       <c r="R9" t="n">
-        <v>6428210</v>
+        <v>6428205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748796</v>
+        <v>122748513</v>
       </c>
       <c r="B10" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,39 +1575,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578916</v>
+        <v>578874</v>
       </c>
       <c r="R10" t="n">
-        <v>6428228</v>
+        <v>6428309</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,6 +1655,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748637</v>
+        <v>122748953</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578855</v>
+        <v>578965</v>
       </c>
       <c r="R11" t="n">
-        <v>6428305</v>
+        <v>6428213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748513</v>
+        <v>122748530</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578874</v>
+        <v>578887</v>
       </c>
       <c r="R12" t="n">
-        <v>6428309</v>
+        <v>6428305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122748770</v>
+        <v>122748865</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578907</v>
+        <v>578923</v>
       </c>
       <c r="R13" t="n">
-        <v>6428303</v>
+        <v>6428196</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748939</v>
+        <v>122748710</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578966</v>
+        <v>578908</v>
       </c>
       <c r="R14" t="n">
-        <v>6428216</v>
+        <v>6428300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122748903</v>
+        <v>122748878</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578994</v>
+        <v>578923</v>
       </c>
       <c r="R15" t="n">
-        <v>6428205</v>
+        <v>6428199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122748838</v>
+        <v>122748778</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>95141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,39 +2241,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2287,13 +2273,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578919</v>
+        <v>578907</v>
       </c>
       <c r="R16" t="n">
-        <v>6428218</v>
+        <v>6428303</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,6 +2317,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122748891</v>
+        <v>122748669</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>91367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,35 +2348,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2397,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578919</v>
+        <v>578951</v>
       </c>
       <c r="R17" t="n">
-        <v>6428209</v>
+        <v>6428317</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122748625</v>
+        <v>122748474</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578926</v>
+        <v>578871</v>
       </c>
       <c r="R18" t="n">
-        <v>6428331</v>
+        <v>6428320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122748450</v>
+        <v>122748922</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,14 +2605,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 5838, Överum, Sm</t>
+          <t>A 5838. Överum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578855</v>
+        <v>578971</v>
       </c>
       <c r="R19" t="n">
-        <v>6428306</v>
+        <v>6428217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122748878</v>
+        <v>122748749</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578923</v>
+        <v>578854</v>
       </c>
       <c r="R20" t="n">
-        <v>6428199</v>
+        <v>6428300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122748865</v>
+        <v>122748891</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578923</v>
+        <v>578919</v>
       </c>
       <c r="R21" t="n">
-        <v>6428196</v>
+        <v>6428209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122748554</v>
+        <v>122748796</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2916,35 +2906,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2952,13 +2946,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578876</v>
+        <v>578916</v>
       </c>
       <c r="R22" t="n">
-        <v>6428319</v>
+        <v>6428228</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,7 +2990,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3018,7 +3011,7 @@
         <v>122748974</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3126,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748530</v>
+        <v>122748852</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,10 +3167,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578887</v>
+        <v>578925</v>
       </c>
       <c r="R24" t="n">
-        <v>6428305</v>
+        <v>6428192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122748922</v>
+        <v>122748608</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,14 +3274,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 5838. Överum, Sm</t>
+          <t>A 5838, Överum, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578971</v>
+        <v>578920</v>
       </c>
       <c r="R25" t="n">
-        <v>6428217</v>
+        <v>6428319</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,10 +3341,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122748710</v>
+        <v>122748838</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,35 +3353,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3396,13 +3393,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578908</v>
+        <v>578919</v>
       </c>
       <c r="R26" t="n">
-        <v>6428300</v>
+        <v>6428218</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3440,7 +3437,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3459,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122748778</v>
+        <v>122748450</v>
       </c>
       <c r="B27" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,29 +3467,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578907</v>
+        <v>578855</v>
       </c>
       <c r="R27" t="n">
-        <v>6428303</v>
+        <v>6428306</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122748474</v>
+        <v>122748802</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,35 +3578,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3614,13 +3618,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578871</v>
+        <v>578916</v>
       </c>
       <c r="R28" t="n">
-        <v>6428320</v>
+        <v>6428228</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3658,7 +3662,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3677,10 +3680,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122748650</v>
+        <v>122748554</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3725,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578934</v>
+        <v>578876</v>
       </c>
       <c r="R29" t="n">
-        <v>6428344</v>
+        <v>6428319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,10 +3791,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122748817</v>
+        <v>122748770</v>
       </c>
       <c r="B30" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,35 +3803,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3836,13 +3839,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578912</v>
+        <v>578907</v>
       </c>
       <c r="R30" t="n">
-        <v>6428250</v>
+        <v>6428303</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3880,6 +3883,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3898,10 +3902,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122748669</v>
+        <v>122748871</v>
       </c>
       <c r="B31" t="n">
-        <v>91365</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,38 +3914,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3949,10 +3950,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578951</v>
+        <v>578921</v>
       </c>
       <c r="R31" t="n">
-        <v>6428317</v>
+        <v>6428203</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122748749</v>
+        <v>122748650</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,10 +4061,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578854</v>
+        <v>578934</v>
       </c>
       <c r="R32" t="n">
-        <v>6428300</v>
+        <v>6428344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,10 +4124,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122748608</v>
+        <v>122748817</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4135,35 +4136,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4171,13 +4172,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578920</v>
+        <v>578912</v>
       </c>
       <c r="R33" t="n">
-        <v>6428319</v>
+        <v>6428250</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4215,7 +4216,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832655</v>
+        <v>122831868</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578894</v>
+        <v>578848</v>
       </c>
       <c r="R34" t="n">
-        <v>6428171</v>
+        <v>6428302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832750</v>
+        <v>122832675</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578986</v>
+        <v>578924</v>
       </c>
       <c r="R35" t="n">
-        <v>6428201</v>
+        <v>6428234</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832231</v>
+        <v>122832592</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578889</v>
+        <v>578925</v>
       </c>
       <c r="R36" t="n">
-        <v>6428243</v>
+        <v>6428157</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832341</v>
+        <v>122832101</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4579,33 +4579,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4615,10 +4611,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578917</v>
+        <v>578875</v>
       </c>
       <c r="R37" t="n">
-        <v>6428212</v>
+        <v>6428259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,10 +4674,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832134</v>
+        <v>122832884</v>
       </c>
       <c r="B38" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4726,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578881</v>
+        <v>578944</v>
       </c>
       <c r="R38" t="n">
-        <v>6428255</v>
+        <v>6428183</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,10 +4785,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832456</v>
+        <v>122832231</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578914</v>
+        <v>578889</v>
       </c>
       <c r="R39" t="n">
-        <v>6428200</v>
+        <v>6428243</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4900,10 +4896,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832675</v>
+        <v>122832077</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578924</v>
+        <v>578858</v>
       </c>
       <c r="R40" t="n">
-        <v>6428234</v>
+        <v>6428260</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5011,10 +5007,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832563</v>
+        <v>122832817</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578948</v>
+        <v>578996</v>
       </c>
       <c r="R41" t="n">
-        <v>6428141</v>
+        <v>6428222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5122,10 +5118,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832702</v>
+        <v>122832650</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5170,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578972</v>
+        <v>578917</v>
       </c>
       <c r="R42" t="n">
-        <v>6428239</v>
+        <v>6428142</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,10 +5229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832254</v>
+        <v>122832550</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5281,10 +5277,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578889</v>
+        <v>578934</v>
       </c>
       <c r="R43" t="n">
-        <v>6428248</v>
+        <v>6428155</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5344,10 +5340,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122831927</v>
+        <v>122832563</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5392,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578836</v>
+        <v>578948</v>
       </c>
       <c r="R44" t="n">
-        <v>6428289</v>
+        <v>6428141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,10 +5451,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832157</v>
+        <v>122832730</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578886</v>
+        <v>578971</v>
       </c>
       <c r="R45" t="n">
-        <v>6428255</v>
+        <v>6428216</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,10 +5562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832383</v>
+        <v>122832530</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5614,10 +5610,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578929</v>
+        <v>578925</v>
       </c>
       <c r="R46" t="n">
-        <v>6428202</v>
+        <v>6428178</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,10 +5673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832530</v>
+        <v>122831927</v>
       </c>
       <c r="B47" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5725,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578925</v>
+        <v>578836</v>
       </c>
       <c r="R47" t="n">
-        <v>6428178</v>
+        <v>6428289</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,10 +5784,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832436</v>
+        <v>122832295</v>
       </c>
       <c r="B48" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5800,39 +5796,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5840,13 +5832,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578943</v>
+        <v>578916</v>
       </c>
       <c r="R48" t="n">
-        <v>6428212</v>
+        <v>6428220</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5884,6 +5876,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5902,10 +5895,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832730</v>
+        <v>122832686</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,7 +5946,7 @@
         <v>578971</v>
       </c>
       <c r="R49" t="n">
-        <v>6428216</v>
+        <v>6428232</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6013,10 +6006,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832662</v>
+        <v>122832846</v>
       </c>
       <c r="B50" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6061,10 +6054,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578900</v>
+        <v>578992</v>
       </c>
       <c r="R50" t="n">
-        <v>6428250</v>
+        <v>6428165</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6124,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832817</v>
+        <v>122832436</v>
       </c>
       <c r="B51" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6136,35 +6129,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6172,13 +6169,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578996</v>
+        <v>578943</v>
       </c>
       <c r="R51" t="n">
-        <v>6428222</v>
+        <v>6428212</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6216,7 +6213,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6235,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832077</v>
+        <v>122832750</v>
       </c>
       <c r="B52" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6283,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578858</v>
+        <v>578986</v>
       </c>
       <c r="R52" t="n">
-        <v>6428260</v>
+        <v>6428201</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6346,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122833108</v>
+        <v>122832456</v>
       </c>
       <c r="B53" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6358,39 +6354,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6398,13 +6390,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578912</v>
+        <v>578914</v>
       </c>
       <c r="R53" t="n">
-        <v>6428250</v>
+        <v>6428200</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6442,6 +6434,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6460,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832550</v>
+        <v>122832134</v>
       </c>
       <c r="B54" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6508,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578934</v>
+        <v>578881</v>
       </c>
       <c r="R54" t="n">
-        <v>6428155</v>
+        <v>6428255</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6571,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832784</v>
+        <v>122833108</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6583,35 +6576,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6619,13 +6616,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578994</v>
+        <v>578912</v>
       </c>
       <c r="R55" t="n">
-        <v>6428231</v>
+        <v>6428250</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6663,7 +6660,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6682,10 +6678,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832986</v>
+        <v>122832768</v>
       </c>
       <c r="B56" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6730,10 +6726,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578944</v>
+        <v>578986</v>
       </c>
       <c r="R56" t="n">
-        <v>6428183</v>
+        <v>6428221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6793,10 +6789,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832846</v>
+        <v>122832341</v>
       </c>
       <c r="B57" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6841,10 +6837,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578992</v>
+        <v>578917</v>
       </c>
       <c r="R57" t="n">
-        <v>6428165</v>
+        <v>6428212</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,10 +6900,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122831868</v>
+        <v>122832662</v>
       </c>
       <c r="B58" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6952,10 +6948,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578848</v>
+        <v>578900</v>
       </c>
       <c r="R58" t="n">
-        <v>6428302</v>
+        <v>6428250</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7015,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832592</v>
+        <v>122832157</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7063,10 +7059,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578925</v>
+        <v>578886</v>
       </c>
       <c r="R59" t="n">
-        <v>6428157</v>
+        <v>6428255</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7126,10 +7122,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832686</v>
+        <v>122832254</v>
       </c>
       <c r="B60" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7174,10 +7170,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578971</v>
+        <v>578889</v>
       </c>
       <c r="R60" t="n">
-        <v>6428232</v>
+        <v>6428248</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7237,10 +7233,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832101</v>
+        <v>122832400</v>
       </c>
       <c r="B61" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7249,29 +7245,33 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578875</v>
+        <v>578935</v>
       </c>
       <c r="R61" t="n">
-        <v>6428259</v>
+        <v>6428215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832400</v>
+        <v>122832383</v>
       </c>
       <c r="B62" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578935</v>
+        <v>578929</v>
       </c>
       <c r="R62" t="n">
-        <v>6428215</v>
+        <v>6428202</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7455,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832768</v>
+        <v>122832208</v>
       </c>
       <c r="B63" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578986</v>
+        <v>578887</v>
       </c>
       <c r="R63" t="n">
-        <v>6428221</v>
+        <v>6428260</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832650</v>
+        <v>122832702</v>
       </c>
       <c r="B64" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578917</v>
+        <v>578972</v>
       </c>
       <c r="R64" t="n">
-        <v>6428142</v>
+        <v>6428239</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832208</v>
+        <v>122832655</v>
       </c>
       <c r="B65" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578887</v>
+        <v>578894</v>
       </c>
       <c r="R65" t="n">
-        <v>6428260</v>
+        <v>6428171</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832295</v>
+        <v>122832784</v>
       </c>
       <c r="B66" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578916</v>
+        <v>578994</v>
       </c>
       <c r="R66" t="n">
-        <v>6428220</v>
+        <v>6428231</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122833108</v>
+        <v>122832768</v>
       </c>
       <c r="B55" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6576,39 +6576,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6616,13 +6612,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578912</v>
+        <v>578986</v>
       </c>
       <c r="R55" t="n">
-        <v>6428250</v>
+        <v>6428221</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6660,6 +6656,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6678,10 +6675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832768</v>
+        <v>122833108</v>
       </c>
       <c r="B56" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6690,35 +6687,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6726,13 +6727,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578986</v>
+        <v>578912</v>
       </c>
       <c r="R56" t="n">
-        <v>6428221</v>
+        <v>6428250</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6770,7 +6771,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122831868</v>
+        <v>122832134</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578848</v>
+        <v>578881</v>
       </c>
       <c r="R34" t="n">
-        <v>6428302</v>
+        <v>6428255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832675</v>
+        <v>122832702</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578924</v>
+        <v>578972</v>
       </c>
       <c r="R35" t="n">
-        <v>6428234</v>
+        <v>6428239</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,7 +4459,7 @@
         <v>122832592</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832101</v>
+        <v>122832655</v>
       </c>
       <c r="B37" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4579,29 +4579,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4611,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578875</v>
+        <v>578894</v>
       </c>
       <c r="R37" t="n">
-        <v>6428259</v>
+        <v>6428171</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4674,10 +4678,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832884</v>
+        <v>122832675</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578944</v>
+        <v>578924</v>
       </c>
       <c r="R38" t="n">
-        <v>6428183</v>
+        <v>6428234</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4785,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832231</v>
+        <v>122832730</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4833,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578889</v>
+        <v>578971</v>
       </c>
       <c r="R39" t="n">
-        <v>6428243</v>
+        <v>6428216</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832077</v>
+        <v>122832530</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4944,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578858</v>
+        <v>578925</v>
       </c>
       <c r="R40" t="n">
-        <v>6428260</v>
+        <v>6428178</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5007,10 +5011,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832817</v>
+        <v>122832400</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5055,10 +5059,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578996</v>
+        <v>578935</v>
       </c>
       <c r="R41" t="n">
-        <v>6428222</v>
+        <v>6428215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832650</v>
+        <v>122832945</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5166,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578917</v>
+        <v>578992</v>
       </c>
       <c r="R42" t="n">
-        <v>6428142</v>
+        <v>6428165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5229,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832550</v>
+        <v>122832686</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5277,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578934</v>
+        <v>578971</v>
       </c>
       <c r="R43" t="n">
-        <v>6428155</v>
+        <v>6428232</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5340,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832563</v>
+        <v>122832817</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5388,10 +5392,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578948</v>
+        <v>578996</v>
       </c>
       <c r="R44" t="n">
-        <v>6428141</v>
+        <v>6428222</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5451,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832730</v>
+        <v>122832383</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5499,10 +5503,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578971</v>
+        <v>578929</v>
       </c>
       <c r="R45" t="n">
-        <v>6428216</v>
+        <v>6428202</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5562,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832530</v>
+        <v>122832563</v>
       </c>
       <c r="B46" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5610,10 +5614,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578925</v>
+        <v>578948</v>
       </c>
       <c r="R46" t="n">
-        <v>6428178</v>
+        <v>6428141</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5673,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122831927</v>
+        <v>122832550</v>
       </c>
       <c r="B47" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5721,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578836</v>
+        <v>578934</v>
       </c>
       <c r="R47" t="n">
-        <v>6428289</v>
+        <v>6428155</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5784,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832295</v>
+        <v>122832436</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>57634</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5796,35 +5800,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5832,13 +5840,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578916</v>
+        <v>578943</v>
       </c>
       <c r="R48" t="n">
-        <v>6428220</v>
+        <v>6428212</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5876,7 +5884,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5895,10 +5902,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832686</v>
+        <v>122832254</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5943,10 +5950,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578971</v>
+        <v>578889</v>
       </c>
       <c r="R49" t="n">
-        <v>6428232</v>
+        <v>6428248</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6006,10 +6013,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122832846</v>
+        <v>122833108</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6018,35 +6025,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6054,13 +6065,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578992</v>
+        <v>578912</v>
       </c>
       <c r="R50" t="n">
-        <v>6428165</v>
+        <v>6428250</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6098,7 +6109,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6117,10 +6127,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832436</v>
+        <v>122832784</v>
       </c>
       <c r="B51" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6129,39 +6139,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6169,13 +6175,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578943</v>
+        <v>578994</v>
       </c>
       <c r="R51" t="n">
-        <v>6428212</v>
+        <v>6428231</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6213,6 +6219,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6231,10 +6238,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832750</v>
+        <v>122832662</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6279,10 +6286,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578986</v>
+        <v>578900</v>
       </c>
       <c r="R52" t="n">
-        <v>6428201</v>
+        <v>6428250</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6342,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832456</v>
+        <v>122832157</v>
       </c>
       <c r="B53" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6390,10 +6397,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578914</v>
+        <v>578886</v>
       </c>
       <c r="R53" t="n">
-        <v>6428200</v>
+        <v>6428255</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6460,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832134</v>
+        <v>122832986</v>
       </c>
       <c r="B54" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6501,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578881</v>
+        <v>578944</v>
       </c>
       <c r="R54" t="n">
-        <v>6428255</v>
+        <v>6428183</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,10 +6571,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832768</v>
+        <v>122832456</v>
       </c>
       <c r="B55" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6612,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578986</v>
+        <v>578914</v>
       </c>
       <c r="R55" t="n">
-        <v>6428221</v>
+        <v>6428200</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,10 +6682,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122833108</v>
+        <v>122832768</v>
       </c>
       <c r="B56" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6687,39 +6694,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6727,13 +6730,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578912</v>
+        <v>578986</v>
       </c>
       <c r="R56" t="n">
-        <v>6428250</v>
+        <v>6428221</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6771,6 +6774,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6789,10 +6793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832341</v>
+        <v>122832295</v>
       </c>
       <c r="B57" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6837,10 +6841,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578917</v>
+        <v>578916</v>
       </c>
       <c r="R57" t="n">
-        <v>6428212</v>
+        <v>6428220</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6900,10 +6904,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832662</v>
+        <v>122832341</v>
       </c>
       <c r="B58" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6948,10 +6952,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578900</v>
+        <v>578917</v>
       </c>
       <c r="R58" t="n">
-        <v>6428250</v>
+        <v>6428212</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7011,10 +7015,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832157</v>
+        <v>122832231</v>
       </c>
       <c r="B59" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7059,10 +7063,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578886</v>
+        <v>578889</v>
       </c>
       <c r="R59" t="n">
-        <v>6428255</v>
+        <v>6428243</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7122,10 +7126,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122832254</v>
+        <v>122831868</v>
       </c>
       <c r="B60" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7170,10 +7174,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578889</v>
+        <v>578848</v>
       </c>
       <c r="R60" t="n">
-        <v>6428248</v>
+        <v>6428302</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7233,10 +7237,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832400</v>
+        <v>122832650</v>
       </c>
       <c r="B61" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7281,10 +7285,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578935</v>
+        <v>578917</v>
       </c>
       <c r="R61" t="n">
-        <v>6428215</v>
+        <v>6428142</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7344,10 +7348,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832383</v>
+        <v>122832077</v>
       </c>
       <c r="B62" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7392,10 +7396,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578929</v>
+        <v>578858</v>
       </c>
       <c r="R62" t="n">
-        <v>6428202</v>
+        <v>6428260</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7458,7 +7462,7 @@
         <v>122832208</v>
       </c>
       <c r="B63" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7566,10 +7570,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122832702</v>
+        <v>122831927</v>
       </c>
       <c r="B64" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,10 +7618,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578972</v>
+        <v>578836</v>
       </c>
       <c r="R64" t="n">
-        <v>6428239</v>
+        <v>6428289</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7677,10 +7681,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832655</v>
+        <v>122832750</v>
       </c>
       <c r="B65" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,10 +7729,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578894</v>
+        <v>578986</v>
       </c>
       <c r="R65" t="n">
-        <v>6428171</v>
+        <v>6428201</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7788,10 +7792,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832784</v>
+        <v>122832101</v>
       </c>
       <c r="B66" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7800,33 +7804,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578994</v>
+        <v>578875</v>
       </c>
       <c r="R66" t="n">
-        <v>6428231</v>
+        <v>6428259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 5838-2025 artfynd.xlsx
+++ b/artfynd/A 5838-2025 artfynd.xlsx
@@ -4234,10 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122832134</v>
+        <v>122832400</v>
       </c>
       <c r="B34" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578881</v>
+        <v>578935</v>
       </c>
       <c r="R34" t="n">
-        <v>6428255</v>
+        <v>6428215</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122832702</v>
+        <v>122832530</v>
       </c>
       <c r="B35" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578972</v>
+        <v>578925</v>
       </c>
       <c r="R35" t="n">
-        <v>6428239</v>
+        <v>6428178</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122832592</v>
+        <v>122832662</v>
       </c>
       <c r="B36" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578925</v>
+        <v>578900</v>
       </c>
       <c r="R36" t="n">
-        <v>6428157</v>
+        <v>6428250</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122832655</v>
+        <v>122832768</v>
       </c>
       <c r="B37" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578894</v>
+        <v>578986</v>
       </c>
       <c r="R37" t="n">
-        <v>6428171</v>
+        <v>6428221</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122832675</v>
+        <v>122831927</v>
       </c>
       <c r="B38" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578924</v>
+        <v>578836</v>
       </c>
       <c r="R38" t="n">
-        <v>6428234</v>
+        <v>6428289</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122832730</v>
+        <v>122832817</v>
       </c>
       <c r="B39" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578971</v>
+        <v>578996</v>
       </c>
       <c r="R39" t="n">
-        <v>6428216</v>
+        <v>6428222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122832530</v>
+        <v>122832341</v>
       </c>
       <c r="B40" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578925</v>
+        <v>578917</v>
       </c>
       <c r="R40" t="n">
-        <v>6428178</v>
+        <v>6428212</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122832400</v>
+        <v>122832702</v>
       </c>
       <c r="B41" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578935</v>
+        <v>578972</v>
       </c>
       <c r="R41" t="n">
-        <v>6428215</v>
+        <v>6428239</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122832945</v>
+        <v>122832655</v>
       </c>
       <c r="B42" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578992</v>
+        <v>578894</v>
       </c>
       <c r="R42" t="n">
-        <v>6428165</v>
+        <v>6428171</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122832686</v>
+        <v>122832846</v>
       </c>
       <c r="B43" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578971</v>
+        <v>578992</v>
       </c>
       <c r="R43" t="n">
-        <v>6428232</v>
+        <v>6428165</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122832817</v>
+        <v>122832592</v>
       </c>
       <c r="B44" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578996</v>
+        <v>578925</v>
       </c>
       <c r="R44" t="n">
-        <v>6428222</v>
+        <v>6428157</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122832383</v>
+        <v>122832563</v>
       </c>
       <c r="B45" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578929</v>
+        <v>578948</v>
       </c>
       <c r="R45" t="n">
-        <v>6428202</v>
+        <v>6428141</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122832563</v>
+        <v>122832077</v>
       </c>
       <c r="B46" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578948</v>
+        <v>578858</v>
       </c>
       <c r="R46" t="n">
-        <v>6428141</v>
+        <v>6428260</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122832550</v>
+        <v>122832675</v>
       </c>
       <c r="B47" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578934</v>
+        <v>578924</v>
       </c>
       <c r="R47" t="n">
-        <v>6428155</v>
+        <v>6428234</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122832436</v>
+        <v>122832750</v>
       </c>
       <c r="B48" t="n">
-        <v>57634</v>
+        <v>98379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5800,39 +5800,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5840,13 +5836,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578943</v>
+        <v>578986</v>
       </c>
       <c r="R48" t="n">
-        <v>6428212</v>
+        <v>6428201</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5884,6 +5880,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5902,10 +5899,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122832254</v>
+        <v>122832884</v>
       </c>
       <c r="B49" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5950,10 +5947,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578889</v>
+        <v>578944</v>
       </c>
       <c r="R49" t="n">
-        <v>6428248</v>
+        <v>6428183</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6013,10 +6010,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122833108</v>
+        <v>122832784</v>
       </c>
       <c r="B50" t="n">
-        <v>57851</v>
+        <v>98379</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6025,39 +6022,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6065,13 +6058,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578912</v>
+        <v>578994</v>
       </c>
       <c r="R50" t="n">
-        <v>6428250</v>
+        <v>6428231</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6109,6 +6102,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6127,10 +6121,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122832784</v>
+        <v>122833108</v>
       </c>
       <c r="B51" t="n">
-        <v>98376</v>
+        <v>57851</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6139,35 +6133,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6175,13 +6173,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578994</v>
+        <v>578912</v>
       </c>
       <c r="R51" t="n">
-        <v>6428231</v>
+        <v>6428250</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6219,7 +6217,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6238,10 +6235,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122832662</v>
+        <v>122832157</v>
       </c>
       <c r="B52" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6286,10 +6283,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578900</v>
+        <v>578886</v>
       </c>
       <c r="R52" t="n">
-        <v>6428250</v>
+        <v>6428255</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6349,10 +6346,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122832157</v>
+        <v>122832134</v>
       </c>
       <c r="B53" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6397,7 +6394,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578886</v>
+        <v>578881</v>
       </c>
       <c r="R53" t="n">
         <v>6428255</v>
@@ -6460,10 +6457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122832986</v>
+        <v>122832436</v>
       </c>
       <c r="B54" t="n">
-        <v>98376</v>
+        <v>57634</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6472,35 +6469,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6508,13 +6509,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578944</v>
+        <v>578943</v>
       </c>
       <c r="R54" t="n">
-        <v>6428183</v>
+        <v>6428212</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6552,7 +6553,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6571,10 +6571,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122832456</v>
+        <v>122831868</v>
       </c>
       <c r="B55" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578914</v>
+        <v>578848</v>
       </c>
       <c r="R55" t="n">
-        <v>6428200</v>
+        <v>6428302</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122832768</v>
+        <v>122832208</v>
       </c>
       <c r="B56" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578986</v>
+        <v>578887</v>
       </c>
       <c r="R56" t="n">
-        <v>6428221</v>
+        <v>6428260</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6793,10 +6793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122832295</v>
+        <v>122832730</v>
       </c>
       <c r="B57" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578916</v>
+        <v>578971</v>
       </c>
       <c r="R57" t="n">
-        <v>6428220</v>
+        <v>6428216</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,10 +6904,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122832341</v>
+        <v>122832686</v>
       </c>
       <c r="B58" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578917</v>
+        <v>578971</v>
       </c>
       <c r="R58" t="n">
-        <v>6428212</v>
+        <v>6428232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122832231</v>
+        <v>122832295</v>
       </c>
       <c r="B59" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7063,10 +7063,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578889</v>
+        <v>578916</v>
       </c>
       <c r="R59" t="n">
-        <v>6428243</v>
+        <v>6428220</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122831868</v>
+        <v>122832550</v>
       </c>
       <c r="B60" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578848</v>
+        <v>578934</v>
       </c>
       <c r="R60" t="n">
-        <v>6428302</v>
+        <v>6428155</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7237,10 +7237,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122832650</v>
+        <v>122832254</v>
       </c>
       <c r="B61" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578917</v>
+        <v>578889</v>
       </c>
       <c r="R61" t="n">
-        <v>6428142</v>
+        <v>6428248</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7348,10 +7348,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122832077</v>
+        <v>122832383</v>
       </c>
       <c r="B62" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578858</v>
+        <v>578929</v>
       </c>
       <c r="R62" t="n">
-        <v>6428260</v>
+        <v>6428202</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7459,10 +7459,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122832208</v>
+        <v>122832101</v>
       </c>
       <c r="B63" t="n">
-        <v>98376</v>
+        <v>95150</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7471,33 +7471,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7507,10 +7503,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578887</v>
+        <v>578875</v>
       </c>
       <c r="R63" t="n">
-        <v>6428260</v>
+        <v>6428259</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7570,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122831927</v>
+        <v>122832231</v>
       </c>
       <c r="B64" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7618,10 +7614,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578836</v>
+        <v>578889</v>
       </c>
       <c r="R64" t="n">
-        <v>6428289</v>
+        <v>6428243</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7681,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122832750</v>
+        <v>122832456</v>
       </c>
       <c r="B65" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7729,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578986</v>
+        <v>578914</v>
       </c>
       <c r="R65" t="n">
-        <v>6428201</v>
+        <v>6428200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7792,10 +7788,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122832101</v>
+        <v>122832650</v>
       </c>
       <c r="B66" t="n">
-        <v>95147</v>
+        <v>98379</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7804,29 +7800,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578875</v>
+        <v>578917</v>
       </c>
       <c r="R66" t="n">
-        <v>6428259</v>
+        <v>6428142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
